--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/PO Rebuild April 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97429E0-4DD2-2144-A530-0F8AE3D33563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8606F-98E9-104A-8C8E-13DB01C3F5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="31120" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="580" yWindow="7080" windowWidth="32940" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="299">
   <si>
     <t>ID</t>
   </si>
@@ -181,9 +181,6 @@
     <t>Definition adopted. Blank until consensus.</t>
   </si>
   <si>
-    <t>Properties adopted. Blank until consensus.</t>
-  </si>
-  <si>
     <t>owl:Class / owl:ObjectProperty / owl:DatatypeProperty / owl:AnnotationProperty / owl:NamedIndividual</t>
   </si>
   <si>
@@ -443,9 +440,6 @@
     <t>CONTRIBUTOR 3  (hidden)</t>
   </si>
   <si>
-    <t>SCOPE &amp; STATUS</t>
-  </si>
-  <si>
     <t>Decision ID</t>
   </si>
   <si>
@@ -494,9 +488,6 @@
     <t>Consensus Status</t>
   </si>
   <si>
-    <t>Affects Terms</t>
-  </si>
-  <si>
     <t>The adopted decision — blank until consensus. Human-written. Never AI content.</t>
   </si>
   <si>
@@ -528,12 +519,6 @@
   </si>
   <si>
     <t>Approved / Rejected / Deferred / Disputed</t>
-  </si>
-  <si>
-    <t>Affected ent IRIs or labels.</t>
-  </si>
-  <si>
-    <t>Proposed / Approved / Superseded</t>
   </si>
   <si>
     <t>Quality Management System for Human-Assured Ontology Development (QMS-HAOD) v1.0</t>
@@ -994,6 +979,183 @@
     <t>Property: isDefinedBy: https://purl.org/cco/[ontology-name] e.g. https://purl.org/cco/person</t>
   </si>
   <si>
+    <t>has birthdate</t>
+  </si>
+  <si>
+    <t>Proposed label for this Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD-001 </t>
+  </si>
+  <si>
+    <t>has birthdate: What type of OWL Property?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I propose 'Object Property' </t>
+  </si>
+  <si>
+    <t>C1: Attestation</t>
+  </si>
+  <si>
+    <t>C2: Attestation</t>
+  </si>
+  <si>
+    <t>C3: Attestation</t>
+  </si>
+  <si>
+    <t>C2: Atestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The choice of Object Property enables the subject ‘Person’ to relate via ‘has birthdate’ to the object ‘birthdate.’  Enables a specific data value without specifying the datatype.  Birthdate is so commonly used, and 'has birthdate' is a needed property, it is good 'has birthdate' will get an IRI. </t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>C1: Aditional Properties</t>
+  </si>
+  <si>
+    <t>C2: Additional Properties</t>
+  </si>
+  <si>
+    <t>C3: Additional Properties</t>
+  </si>
+  <si>
+    <t>Protégé v5.6.7</t>
+  </si>
+  <si>
+    <t>Each instance of Person has an instance of Birthdate.</t>
+  </si>
+  <si>
+    <t>Single contributor — no objections raised. Open for additional contributor review.</t>
+  </si>
+  <si>
+    <t>AD-002</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000046</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000061</t>
+  </si>
+  <si>
+    <t>PersonOntology</t>
+  </si>
+  <si>
+    <t>Concluded By
+(name, date)</t>
+  </si>
+  <si>
+    <t>J. Schoening, 2026-04-19</t>
+  </si>
+  <si>
+    <t>has birthdate will be an Object Property</t>
+  </si>
+  <si>
+    <t>Parent IRI adopted. Blank until consensus.
+owl:Class: rdfs:subClassOf IRI
+owl:ObjectProperty: rdfs:subPropertyOf IRI (optional)
+owl:DatatypeProperty: rdfs:subPropertyOf IRI (optional)
+owl:AnnotationProperty: rdfs:subPropertyOf IRI (optional)
+owl:NamedIndividual: rdf:type IRI (additional types beyond primary OWL type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skos:altLabel Date of Birth (used by SEMIC) and DOB (commonly abbbreviation); dcterms:created with date added to ontology file.; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity Tab: Consensus Position </t>
+  </si>
+  <si>
+    <t>CCO-Domains / Global Research, Inc. (501c3) | https://github.com/cco-domains/cco-domains | BSD-3-Clause</t>
+  </si>
+  <si>
+    <t>skos:altLabel 'hasBirthdate'; rdfs:domain (Person and IRI) ; rdfs:range (ent00000046); dcterm: created</t>
+  </si>
+  <si>
+    <t>AD-003</t>
+  </si>
+  <si>
+    <t>Since we are rebuilding 3 domain ontologies we don't want pre-existing IRIs to influence decisions, but if a new entity completes the QMS process and needs an IRI, it would be better to use the pre-existing IRI so as not to impact current developers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I propose deleting all prior IRIs from registry except ent00000046 and ent00000061, and not refering to these IRIs or labels when rebuilding and expanding any of the domain ontologies.  Only AFTER a new entity has been through the QMS process and approved, it should be issued an IRI, and if there was a previous IRI with the same semantics, it may use that IRI to avoid impacting current users. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensures the QMS process is followed and completed without influence from pre-existing IRIs.  Also permits reuse of legacy IRIs to minimize impact on current users. </t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — J. Schoening, 2026-04-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete all IRIs from registry except ent00000046 and ent00000061.  Ensure QMS process is completed before issuing an IRI.  If legacy IRI for same or similar entitiy is still available, may use the IRI. </t>
+  </si>
+  <si>
+    <t>Social Security Number</t>
+  </si>
+  <si>
+    <t>https://www.ssa.gov/employer/ssnvshandbk/glossary.htm</t>
+  </si>
+  <si>
+    <t>Social Security Number; a unique nine (9)-digit number assigned by SSA to identify an individual when reporting wages, paying taxes and collecting benefits.</t>
+  </si>
+  <si>
+    <t>US Social Security Administration</t>
+  </si>
+  <si>
+    <t>Person Identifier</t>
+  </si>
+  <si>
+    <t>AD-004</t>
+  </si>
+  <si>
+    <t>How to add SSN with stable IRI to support current users</t>
+  </si>
+  <si>
+    <t>PersonIdentifier (New Class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://purl.org/cco/ont00000649 ; rdfs:label Non-Name Identifier </t>
+  </si>
+  <si>
+    <t>A non-Name Identifier for a person.</t>
+  </si>
+  <si>
+    <t>AD-005</t>
+  </si>
+  <si>
+    <t>Person Identity (see AD-0004 above).</t>
+  </si>
+  <si>
+    <t>There are many categories of identifiers for a person.  It would be too much work at this early stage to research all these categories to develop a comprehensive solution, so since SSN is needed now, all that should be added now is PersonIdentifier and then SSN.  A more comprehensive solution should be left until it is needed and we have the contributors and time to develop it.</t>
+  </si>
+  <si>
+    <t>See AD-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See AD-004.  </t>
+  </si>
+  <si>
+    <t>There are many categories of identifiers for many types of persons, organizations, and other things.  It would be too much work at this early stage to research all these categories to develop a comprehensive solution, even for just PersonIdentifiers, so since SSN is needed now, that will be all that is added and given a stable IRI.  A comprehensive solution should be left until its needed and we have the contributors and time to develop it, perhaps in stages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I propose adding SSN as subclass of a new PersonIdentifier in PersonOntology, a subclass of Non-Name Identifier (ont00000649), and improving on this hierarchy later. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add SSN as subclass of a new PersonIdentifier in PersonOntology, a subclass of Non-Name Identifier (ont00000649), and improving on this hierarchy later. </t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000008</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Person Identifier issued by the U.S. Social Security Administration. </t>
+  </si>
+  <si>
+    <t>A Person Identifier issued by the U.S. Social Security Administration.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1004,7 +1166,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>List additional properties asserted on this entity.</t>
+      <t>All entities shall  include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   
+List additional properties asserted on this entity.</t>
     </r>
     <r>
       <rPr>
@@ -1048,7 +1211,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">skos:altLabel; skos:scopeNote; skos:example; skos:exactMatch; skos:closeMatch; dcterms:created; dcterms:source
+      <t xml:space="preserve">skos:altLabel; skos:scopeNote; skos:example; skos:exactMatch; skos:closeMatch; dcterms:source
 </t>
     </r>
     <r>
@@ -1098,103 +1261,127 @@
     </r>
   </si>
   <si>
-    <t>has birthdate</t>
-  </si>
-  <si>
-    <t>Proposed label for this Entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD-001 </t>
-  </si>
-  <si>
-    <t>has birthdate: What type of OWL Property?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I propose 'Object Property' </t>
-  </si>
-  <si>
-    <t>C1: Attestation</t>
-  </si>
-  <si>
-    <t>C2: Attestation</t>
-  </si>
-  <si>
-    <t>C3: Attestation</t>
-  </si>
-  <si>
-    <t>C2: Atestation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The choice of Object Property enables the subject ‘Person’ to relate via ‘has birthdate’ to the object ‘birthdate.’  Enables a specific data value without specifying the datatype.  Birthdate is so commonly used, and 'has birthdate' is a needed property, it is good 'has birthdate' will get an IRI. </t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>C1: Aditional Properties</t>
-  </si>
-  <si>
-    <t>C2: Additional Properties</t>
-  </si>
-  <si>
-    <t>C3: Additional Properties</t>
-  </si>
-  <si>
-    <t>Protégé v5.6.7</t>
-  </si>
-  <si>
-    <t>f79bea91c26832afb3d08c1a5e50e71a6347351f</t>
-  </si>
-  <si>
-    <t>Each instance of Person has an instance of Birthdate.</t>
-  </si>
-  <si>
-    <t>Single contributor — no objections raised. Open for additional contributor review.</t>
-  </si>
-  <si>
-    <t>AD-002</t>
-  </si>
-  <si>
-    <t>Definition probably needs improvement.</t>
-  </si>
-  <si>
-    <t>https://purl.org/cco/ent00000046</t>
-  </si>
-  <si>
-    <t>https://purl.org/cco/ent00000061</t>
-  </si>
-  <si>
-    <t>PersonOntology</t>
-  </si>
-  <si>
-    <t>Concluded By
-(name, date)</t>
-  </si>
-  <si>
-    <t>J. Schoening, 2026-04-19</t>
-  </si>
-  <si>
-    <t>has birthdate will be an Object Property</t>
-  </si>
-  <si>
-    <t>Parent IRI adopted. Blank until consensus.
-owl:Class: rdfs:subClassOf IRI
-owl:ObjectProperty: rdfs:subPropertyOf IRI (optional)
-owl:DatatypeProperty: rdfs:subPropertyOf IRI (optional)
-owl:AnnotationProperty: rdfs:subPropertyOf IRI (optional)
-owl:NamedIndividual: rdf:type IRI (additional types beyond primary OWL type)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:altLabel Date of Birth (used by SEMIC) and DOB (commonly abbbreviation); dcterms:created with date added to ontology file.; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entity Tab: Consensus Position </t>
-  </si>
-  <si>
-    <t>CCO-Domains / Global Research, Inc. (501c3) | https://github.com/cco-domains/cco-domains | BSD-3-Clause</t>
-  </si>
-  <si>
-    <t>skos:altLabel 'hasBirthdate'; rdfs:domain (Person and IRI) ; rdfs:range (ent00000046); dcterm: created</t>
+    <t xml:space="preserve">Properties adopted. Blank until consensus.  All entities shall  include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   </t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000062; rdfs:label Person Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skos:altLabel (SSN); skos:example (123-45-6789); </t>
+  </si>
+  <si>
+    <t>feeb029bf7f103bfb77d69989cc67413786577b1</t>
+  </si>
+  <si>
+    <t>skos:altLabel (SSN); skos:example (123-45-6789);   dcterms:source &lt;https://www.ssa.gov/employer/ssnvshandbk/glossary.htm&gt;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>All entities shall include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   
+List additional properties asserted on this entity.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>All entity types:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">skos:altLabel; skos:scopeNote; skos:example; skos:exactMatch; skos:closeMatch; dcterms:source
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">owl:Class only: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">owl:disjointWith
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">owl:ObjectProperty and owl:DatatypeProperty only: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF633806"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rdfs:domain; rdfs:range; rdfs:subPropertyOf; owl:FunctionalProperty; owl:inverseOf</t>
+    </r>
+  </si>
+  <si>
+    <t>skos:altLabel "PersonIdentifier"</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1358,6 +1545,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1458,7 +1659,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1544,9 +1745,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1555,7 +1758,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1571,7 +1773,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1878,7 +2085,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1911,56 +2118,57 @@
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
-    <col min="33" max="34" width="16" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="34" width="16.1640625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="28"/>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="36" t="s">
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="41" t="s">
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="35" t="s">
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="35" t="s">
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="36" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1972,10 +2180,10 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -1999,13 +2207,13 @@
         <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>19</v>
@@ -2020,13 +2228,13 @@
         <v>22</v>
       </c>
       <c r="S2" s="31" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="T2" s="31" t="s">
         <v>23</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="V2" s="30" t="s">
         <v>24</v>
@@ -2041,16 +2249,16 @@
         <v>27</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AA2" s="30" t="s">
         <v>28</v>
       </c>
       <c r="AB2" s="30" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AD2" s="5" t="s">
         <v>30</v>
@@ -2079,207 +2287,328 @@
         <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="K3" s="9" t="s">
+      <c r="R3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="T3" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="O3" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="P3" s="32" t="s">
+      <c r="U3" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="W3" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Y3" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="Z3" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA3" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="T3" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="W3" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="AA3" s="29" t="s">
-        <v>46</v>
-      </c>
       <c r="AB3" s="29" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="H4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K4" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="L4" t="s">
+        <v>259</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC4" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE4" t="s">
         <v>213</v>
       </c>
-      <c r="C4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="AG4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G5" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="H5" t="s">
+        <v>234</v>
+      </c>
+      <c r="I5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J5" t="s">
+        <v>254</v>
+      </c>
+      <c r="K5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="N5" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC5" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH5" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J6" t="s">
+        <v>254</v>
+      </c>
+      <c r="K6" t="s">
+        <v>276</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="N6" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="AC6" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE6" t="s">
         <v>213</v>
       </c>
-      <c r="I4" t="s">
-        <v>217</v>
-      </c>
-      <c r="J4" t="s">
-        <v>262</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="AF6" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="F7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G7" t="s">
+        <v>278</v>
+      </c>
+      <c r="H7" t="s">
+        <v>273</v>
+      </c>
+      <c r="I7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K7" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="L7" t="s">
+        <v>298</v>
+      </c>
+      <c r="M7" t="s">
+        <v>278</v>
+      </c>
+      <c r="N7" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="M4" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="AC4" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>257</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>218</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>254</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>255</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AC7" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD7" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
-      <c r="A5" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="H5" t="s">
-        <v>240</v>
-      </c>
-      <c r="I5" t="s">
-        <v>233</v>
-      </c>
-      <c r="J5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K5" t="s">
-        <v>225</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="AC5" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>218</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>250</v>
-      </c>
+      <c r="AE7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>283</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="J8" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2296,6 +2625,11 @@
     <hyperlink ref="K4" r:id="rId2" xr:uid="{4456617F-A4DD-0A4F-A2A9-20EA9A6A57BE}"/>
     <hyperlink ref="A4" r:id="rId3" xr:uid="{C2E0D389-8646-9D4E-8DE0-EE0E7D01F4F4}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{0E5BDF8E-5FBA-EB42-93AF-68AF9E731350}"/>
+    <hyperlink ref="K7" r:id="rId5" xr:uid="{CEC8E265-A61C-EC44-8135-B61F6A1D8927}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{06654709-EA76-9046-BCA5-5030448CEDA2}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{F715CFF6-2450-C147-AFFC-E28965D2A8E8}"/>
+    <hyperlink ref="A7" r:id="rId8" xr:uid="{A535E8D6-31F3-854F-BE9C-D93CAF050893}"/>
+    <hyperlink ref="E6" r:id="rId9" xr:uid="{237EF0DE-7C02-0244-9D72-7855E59E8D5A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2306,7 +2640,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2322,316 +2656,345 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="J2" s="17" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="I3" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" t="s">
         <v>174</v>
       </c>
-      <c r="E4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" t="s">
-        <v>179</v>
-      </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H4" s="23">
         <v>46120</v>
       </c>
       <c r="J4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
         <v>182</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>181</v>
-      </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H5" s="23">
         <v>46120</v>
       </c>
       <c r="J5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" t="s">
         <v>184</v>
-      </c>
-      <c r="C6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" t="s">
-        <v>189</v>
       </c>
       <c r="H6" s="23">
         <v>46120</v>
       </c>
       <c r="J6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" t="s">
         <v>182</v>
       </c>
-      <c r="C7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>187</v>
-      </c>
-      <c r="F7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>192</v>
       </c>
       <c r="H7" s="23">
         <v>46120</v>
       </c>
       <c r="J7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H8" s="23">
         <v>46121</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" t="s">
         <v>182</v>
       </c>
-      <c r="C9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" t="s">
-        <v>187</v>
-      </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H9" s="23">
         <v>46121</v>
       </c>
       <c r="I9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="224" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H10" s="23">
         <v>46121</v>
       </c>
       <c r="J10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>252</v>
+      </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" t="s">
         <v>211</v>
-      </c>
-      <c r="E11" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11" t="s">
-        <v>216</v>
       </c>
       <c r="H11" s="23">
         <v>46121</v>
       </c>
       <c r="J11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
+        <v>253</v>
+      </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="G12" t="s">
         <v>211</v>
-      </c>
-      <c r="E12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="G12" t="s">
-        <v>216</v>
       </c>
       <c r="H12" s="23">
         <v>46123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="23">
+        <v>46131</v>
       </c>
     </row>
   </sheetData>
@@ -2643,6 +3006,9 @@
     <hyperlink ref="G7" r:id="rId1" xr:uid="{B102BE11-6B79-F145-95E1-65F524A01359}"/>
     <hyperlink ref="G8" r:id="rId2" location="gid=1379912258" xr:uid="{661D4BE0-50A9-5A4A-B7F3-638D66DCA9EE}"/>
     <hyperlink ref="G9" r:id="rId3" location="StandardClaims" xr:uid="{9F358A18-DEC3-774C-87A6-14E16ED08D87}"/>
+    <hyperlink ref="A11" r:id="rId4" xr:uid="{E700B029-EDF2-A045-AF52-4989B15A9704}"/>
+    <hyperlink ref="A12" r:id="rId5" xr:uid="{3EA5242D-920D-604D-B0E9-6F5ADEE2537F}"/>
+    <hyperlink ref="G13" r:id="rId6" xr:uid="{C04B92CB-055B-1549-9C7C-1350ECD0911C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2687,138 +3053,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="35" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="42" t="s">
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="44" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="45" t="s">
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41" t="s">
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="43" t="s">
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
     </row>
     <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="AC2" s="6" t="s">
         <v>36</v>
@@ -2832,97 +3198,97 @@
     </row>
     <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="P3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="10" t="s">
+      <c r="R3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="T3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="U3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="X3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="S3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="T3" s="11" t="s">
+      <c r="Y3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Z3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="AA3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE3" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="AC3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE3" s="12" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2945,7 +3311,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -2966,91 +3332,85 @@
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="24" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="35" t="s">
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="42" t="s">
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="44" t="s">
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="45" t="s">
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+    </row>
+    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="35" t="s">
+      <c r="B2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="T1" s="40"/>
-    </row>
-    <row r="2" spans="1:20" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>29</v>
@@ -3059,161 +3419,226 @@
         <v>30</v>
       </c>
       <c r="R2" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="I3" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="L3" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="N3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>236</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="96" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>242</v>
       </c>
       <c r="B4" s="16">
         <v>46129</v>
       </c>
       <c r="C4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="G4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="P4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="R4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46131</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H5" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="P5" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q5" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="R5" t="s">
         <v>244</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="P4" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="R4" t="s">
+    </row>
+    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46131</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="P6" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q6" s="26" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="128" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="112" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B10" s="16">
         <v>46123</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="R10" t="s">
-        <v>250</v>
-      </c>
-      <c r="S10" t="s">
-        <v>259</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="16">
+        <v>46131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="S1:T1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
@@ -3232,102 +3657,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/PO Rebuild April 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8606F-98E9-104A-8C8E-13DB01C3F5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE41C7CB-BE2A-014D-A072-0E14F24AD2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="580" yWindow="7080" windowWidth="32940" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="300">
   <si>
     <t>ID</t>
   </si>
@@ -1382,6 +1382,9 @@
   </si>
   <si>
     <t>skos:altLabel "PersonIdentifier"</t>
+  </si>
+  <si>
+    <t>ab1385a32e4ccd24550b81ce1554fe56952ac2a9</t>
   </si>
 </sst>
 </file>
@@ -2547,6 +2550,12 @@
       <c r="AG6" t="s">
         <v>248</v>
       </c>
+      <c r="AH6" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
@@ -2605,6 +2614,12 @@
       </c>
       <c r="AG7" t="s">
         <v>248</v>
+      </c>
+      <c r="AH7" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/PO Rebuild April 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE41C7CB-BE2A-014D-A072-0E14F24AD2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E115BE2-B380-C143-9039-D84A47FE0B73}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="7080" windowWidth="32940" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1580" yWindow="1680" windowWidth="32480" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="318">
   <si>
     <t>ID</t>
   </si>
@@ -214,10 +214,6 @@
     <t>Source Type</t>
   </si>
   <si>
-    <t>Verbatim Content
-(paste exactly — no paraphrasing)</t>
-  </si>
-  <si>
     <t>Source URL / Citation
 or Document Reference</t>
   </si>
@@ -233,9 +229,6 @@
   </si>
   <si>
     <t>e.g. Claude Pro / Claude Haiku / Schema.org / FHIR R4 / RFC 9553 / SNOMED CT / ICAO / FBI NCIC / Wikipedia / Prior Discussion</t>
-  </si>
-  <si>
-    <t>VERBATIM. Paste exactly as found. Do not paraphrase, summarize, or evaluate. Contributors naturally bring prior knowledge and hypotheses — sources collected to confirm an initial intuition are equally valid inputs for all contributors to evaluate. The structure — multiple sources, multiple contributors — provides protection against any single contributor's bias determining the outcome.</t>
   </si>
   <si>
     <t>URL, citation, or document reference. For GenAI: note session or document name.</t>
@@ -615,9 +608,6 @@
   </si>
   <si>
     <t>birthdate</t>
-  </si>
-  <si>
-    <t>HL&amp; FHIR</t>
   </si>
   <si>
     <t>date of birth</t>
@@ -891,12 +881,6 @@
     <t>OWL Class adopted</t>
   </si>
   <si>
-    <t>https://purl.org/cco/ont00001340 ; Calendar Date Identifier</t>
-  </si>
-  <si>
-    <t>https://purl.org/cco/ont00001340 ; rdfs:label Calendar Date Identifier</t>
-  </si>
-  <si>
     <t>hasBirthdate</t>
   </si>
   <si>
@@ -958,9 +942,6 @@
     <t>Property</t>
   </si>
   <si>
-    <t>Definition / Parent Class Option / Controlled Vocabulary / Alignment / Candidate Term / Conversation Thread / Architectural Option / Poperty</t>
-  </si>
-  <si>
     <t>owl:ObjectProperty</t>
   </si>
   <si>
@@ -1111,12 +1092,6 @@
     <t>How to add SSN with stable IRI to support current users</t>
   </si>
   <si>
-    <t>PersonIdentifier (New Class)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://purl.org/cco/ont00000649 ; rdfs:label Non-Name Identifier </t>
-  </si>
-  <si>
     <t>A non-Name Identifier for a person.</t>
   </si>
   <si>
@@ -1154,6 +1129,36 @@
   </si>
   <si>
     <t>A Person Identifier issued by the U.S. Social Security Administration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Properties adopted. Blank until consensus.  All entities shall  include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">skos:altLabel (SSN); skos:example (123-45-6789); </t>
+  </si>
+  <si>
+    <t>feeb029bf7f103bfb77d69989cc67413786577b1</t>
+  </si>
+  <si>
+    <t>skos:altLabel (SSN); skos:example (123-45-6789);   dcterms:source &lt;https://www.ssa.gov/employer/ssnvshandbk/glossary.htm&gt;</t>
+  </si>
+  <si>
+    <t>skos:altLabel "PersonIdentifier"</t>
+  </si>
+  <si>
+    <t>ab1385a32e4ccd24550b81ce1554fe56952ac2a9</t>
+  </si>
+  <si>
+    <t>AD-006</t>
+  </si>
+  <si>
+    <t>FullName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I propose we do not have a Person Name as a parent class of the short list of forms of person names.  </t>
+  </si>
+  <si>
+    <t>Full Name</t>
   </si>
   <si>
     <r>
@@ -1166,7 +1171,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>All entities shall  include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   
+      <t>All entities shall include dcterms:created so no need to include in cells below:   
 List additional properties asserted on this entity.</t>
     </r>
     <r>
@@ -1261,130 +1266,76 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Properties adopted. Blank until consensus.  All entities shall  include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   </t>
-  </si>
-  <si>
-    <t>https://purl.org/cco/ent00000062; rdfs:label Person Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:altLabel (SSN); skos:example (123-45-6789); </t>
-  </si>
-  <si>
-    <t>feeb029bf7f103bfb77d69989cc67413786577b1</t>
-  </si>
-  <si>
-    <t>skos:altLabel (SSN); skos:example (123-45-6789);   dcterms:source &lt;https://www.ssa.gov/employer/ssnvshandbk/glossary.htm&gt;</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <u/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>All entities shall include rdfs:isDefinedBy and dcterms:created so no need to include in cells below:   
-List additional properties asserted on this entity.</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <u/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>All entity types:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">skos:altLabel; skos:scopeNote; skos:example; skos:exactMatch; skos:closeMatch; dcterms:source
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <u/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">owl:Class only: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">owl:disjointWith
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <u/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">owl:ObjectProperty and owl:DatatypeProperty only: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF633806"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>rdfs:domain; rdfs:range; rdfs:subPropertyOf; owl:FunctionalProperty; owl:inverseOf</t>
-    </r>
-  </si>
-  <si>
-    <t>skos:altLabel "PersonIdentifier"</t>
-  </si>
-  <si>
-    <t>ab1385a32e4ccd24550b81ce1554fe56952ac2a9</t>
+    <t xml:space="preserve">A Designative Name comprising all or most of a person's various names, e.g. Given Name, Alternate Name, Family Name, etc. but may include initials for some names, as presented by the individual, who may give different versions at different times.  </t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — J. Schoening, 2026-04-22</t>
+  </si>
+  <si>
+    <t>J. Schoening, 2026-04-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Candidate terms spreadsheet there is no other data model that had an intermediate Person Name.  This is a simplistic part of Person Ontology, since these names are a weak form of identity.  In AD-004, we did create a Person Identity parent class, but that was because we anticipate the needs for some deep ontological work under that new class, since identity is so complex and important. </t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000001</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ont00001340 (Calendar Date Identifier)</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000062 (Person Identifier)</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ont00000649 (Non-Name Identifier)</t>
+  </si>
+  <si>
+    <t>Proposed</t>
+  </si>
+  <si>
+    <t>HL7 FHIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defer work on Person Identity. </t>
+  </si>
+  <si>
+    <t>There are many categories of identifiers for a person.  It would be too much work at this early stage to research all these categories to develop a comprehensive solution.</t>
+  </si>
+  <si>
+    <t>Deferred</t>
+  </si>
+  <si>
+    <t>Should we have an intermediate 'Person Name' class between Designative Name' and the various forms of person names</t>
+  </si>
+  <si>
+    <t>No Person Name as parent class of other names for a person.  Instead, all person names are subclasses of Designative Name ont00000003</t>
+  </si>
+  <si>
+    <t>VERBATIM. Paste exactly as found. Do not paraphrase, summarize, or evaluate. Contributors naturally bring prior knowledge and hypotheses — sources collected to confirm an initial intuition are equally valid inputs for all contributors to evaluate. The structure — multiple sources, multiple contributors — provides protection against any single contributor's bias determining the outcome.  Exception: for Candidate Terms rows, enter "Row [N] — [label]" and provide the sheet URL. The Candidate Terms spreadsheet is treated as a structured reference source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source Content </t>
+  </si>
+  <si>
+    <t>Definition / Parent Class Option / Controlled Vocabulary / Alignment / Candidate Term / Conversation Thread / Architectural Option / Poperty/Candidate Terms Row (at https://github.com/cco-domains/cco-domains/blob/rebuild-qms/qms/Candidate%20Terms.xlsx)(Row numbers may change)</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 10 (FullName)</t>
+  </si>
+  <si>
+    <t>Candidate Terms</t>
+  </si>
+  <si>
+    <t>Data Aggregation spreadsheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See many examples in this row.  Many use label 'name' for full name.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 10 (FullName) </t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ont00000003 (Designative Name)</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1345,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1554,14 +1505,6 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1662,7 +1605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1709,7 +1652,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1749,6 +1691,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1776,12 +1730,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2117,7 +2065,7 @@
     <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="26" customWidth="1"/>
+    <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
@@ -2127,51 +2075,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="H1" s="43" t="s">
+      <c r="C1" s="27"/>
+      <c r="H1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="38" t="s">
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="40" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="42" t="s">
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="36" t="s">
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AF1" s="42"/>
+      <c r="AG1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="36" t="s">
+      <c r="AH1" s="42"/>
+      <c r="AI1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2183,10 +2131,10 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>216</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -2210,58 +2158,58 @@
         <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O2" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="31" t="s">
+      <c r="P2" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="31" t="s">
+      <c r="Q2" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="31" t="s">
+      <c r="R2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="T2" s="31" t="s">
+      <c r="S2" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="T2" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="V2" s="30" t="s">
+      <c r="U2" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="V2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="30" t="s">
+      <c r="W2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="30" t="s">
+      <c r="X2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="Y2" s="30" t="s">
+      <c r="Y2" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="AA2" s="30" t="s">
+      <c r="Z2" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA2" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>241</v>
+      <c r="AB2" s="29" t="s">
+        <v>235</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AD2" s="5" t="s">
         <v>30</v>
@@ -2290,340 +2238,399 @@
         <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>42</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M3" s="9" t="s">
         <v>45</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O3" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="P3" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="O3" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="P3" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="R3" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="T3" s="32" t="s">
+      <c r="S3" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="T3" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="W3" s="29" t="s">
+      <c r="U3" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="V3" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="W3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="29" t="s">
+      <c r="X3" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="29" t="s">
+      <c r="Y3" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="AA3" s="29" t="s">
+      <c r="Z3" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA3" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AB3" s="29" t="s">
-        <v>231</v>
+      <c r="AB3" s="28" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>252</v>
+      <c r="A4" s="17" t="s">
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E4" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J4" t="s">
+        <v>248</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="L4" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="N4" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC4" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>285</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
         <v>222</v>
       </c>
-      <c r="F4" t="s">
-        <v>259</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="H4" t="s">
-        <v>208</v>
-      </c>
-      <c r="I4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4" t="s">
-        <v>254</v>
-      </c>
-      <c r="K4" s="49" t="s">
+      <c r="D5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="H5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" t="s">
+        <v>248</v>
+      </c>
+      <c r="K5" t="s">
+        <v>217</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="M5" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="L4" t="s">
-        <v>259</v>
-      </c>
-      <c r="M4" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="AC4" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="N5" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC5" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="AE4" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG4" t="s">
+      <c r="AD5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>285</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" t="s">
         <v>248</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="E6" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J6" t="s">
+        <v>248</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="AC6" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD6" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>274</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH6" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+      <c r="A7" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="B7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G7" t="s">
+        <v>270</v>
+      </c>
+      <c r="H7" t="s">
+        <v>267</v>
+      </c>
+      <c r="I7" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" t="s">
+        <v>248</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="L7" t="s">
+        <v>287</v>
+      </c>
+      <c r="M7" t="s">
+        <v>270</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="AC7" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD7" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>275</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH7" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+      <c r="A8" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="H8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I8" t="s">
+        <v>209</v>
+      </c>
+      <c r="J8" t="s">
+        <v>248</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="L8" t="s">
+        <v>217</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="N8" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AC8" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="AD8" s="25" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="H5" t="s">
-        <v>234</v>
-      </c>
-      <c r="I5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J5" t="s">
-        <v>254</v>
-      </c>
-      <c r="K5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="AC5" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH5" s="50" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="B6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="H6" t="s">
-        <v>269</v>
-      </c>
-      <c r="I6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J6" t="s">
-        <v>254</v>
-      </c>
-      <c r="K6" t="s">
-        <v>276</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="AC6" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>213</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>282</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH6" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D7" t="s">
-        <v>254</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" t="s">
-        <v>278</v>
-      </c>
-      <c r="H7" t="s">
-        <v>273</v>
-      </c>
-      <c r="I7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" t="s">
-        <v>254</v>
-      </c>
-      <c r="K7" s="49" t="s">
-        <v>277</v>
-      </c>
-      <c r="L7" t="s">
-        <v>298</v>
-      </c>
-      <c r="M7" t="s">
-        <v>278</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="AC7" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>213</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>283</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH7" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="J8" s="48"/>
+      <c r="AE8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>275</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>302</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2637,14 +2644,18 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{3CAE867B-5F1C-884C-BA2B-06EB380624C2}"/>
-    <hyperlink ref="K4" r:id="rId2" xr:uid="{4456617F-A4DD-0A4F-A2A9-20EA9A6A57BE}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{C2E0D389-8646-9D4E-8DE0-EE0E7D01F4F4}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{0E5BDF8E-5FBA-EB42-93AF-68AF9E731350}"/>
-    <hyperlink ref="K7" r:id="rId5" xr:uid="{CEC8E265-A61C-EC44-8135-B61F6A1D8927}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{06654709-EA76-9046-BCA5-5030448CEDA2}"/>
-    <hyperlink ref="A6" r:id="rId7" xr:uid="{F715CFF6-2450-C147-AFFC-E28965D2A8E8}"/>
-    <hyperlink ref="A7" r:id="rId8" xr:uid="{A535E8D6-31F3-854F-BE9C-D93CAF050893}"/>
-    <hyperlink ref="E6" r:id="rId9" xr:uid="{237EF0DE-7C02-0244-9D72-7855E59E8D5A}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{C2E0D389-8646-9D4E-8DE0-EE0E7D01F4F4}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{0E5BDF8E-5FBA-EB42-93AF-68AF9E731350}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{06654709-EA76-9046-BCA5-5030448CEDA2}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{F715CFF6-2450-C147-AFFC-E28965D2A8E8}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{A535E8D6-31F3-854F-BE9C-D93CAF050893}"/>
+    <hyperlink ref="E6" r:id="rId7" xr:uid="{237EF0DE-7C02-0244-9D72-7855E59E8D5A}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{6021D980-3517-934B-A08E-2EF5EEA1AE85}"/>
+    <hyperlink ref="K4" r:id="rId9" xr:uid="{78A4C683-D456-6F47-A568-AA315E7CA012}"/>
+    <hyperlink ref="K7" r:id="rId10" xr:uid="{25659D1A-DEBC-F84A-BB3D-5D47FA2BB9A5}"/>
+    <hyperlink ref="K6" r:id="rId11" xr:uid="{796DC518-82D5-9242-AF71-52FCF4FF1621}"/>
+    <hyperlink ref="K8" r:id="rId12" xr:uid="{F2EF0387-CEC0-2D4C-8F4A-37D39AF7718C}"/>
+    <hyperlink ref="E8" r:id="rId13" xr:uid="{1ACF9A50-674F-4E41-96DB-E96B0264622A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2655,39 +2666,39 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="232.1640625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="13" style="23" customWidth="1"/>
+    <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="36" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>49</v>
@@ -2702,314 +2713,349 @@
         <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H4" s="22">
+        <v>46120</v>
+      </c>
+      <c r="J4" t="s">
         <v>171</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="23">
-        <v>46120</v>
-      </c>
-      <c r="J4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="22">
+        <v>46120</v>
+      </c>
+      <c r="J5" t="s">
         <v>171</v>
-      </c>
-      <c r="D5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="G5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="23">
-        <v>46120</v>
-      </c>
-      <c r="J5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" t="s">
         <v>179</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" s="22">
+        <v>46120</v>
+      </c>
+      <c r="J6" t="s">
         <v>171</v>
-      </c>
-      <c r="D6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="G6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H6" s="23">
-        <v>46120</v>
-      </c>
-      <c r="J6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" s="22">
+        <v>46120</v>
+      </c>
+      <c r="J7" t="s">
         <v>171</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" t="s">
         <v>189</v>
       </c>
-      <c r="E7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G8" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H7" s="23">
-        <v>46120</v>
-      </c>
-      <c r="J7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" s="22">
+        <v>46121</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="H8" s="23">
-        <v>46121</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>195</v>
-      </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>198</v>
+        <v>196</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="22">
+        <v>46121</v>
+      </c>
+      <c r="I9" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="H9" s="23">
-        <v>46121</v>
-      </c>
-      <c r="I9" t="s">
-        <v>200</v>
-      </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H10" s="22">
+        <v>46121</v>
+      </c>
+      <c r="J10" t="s">
         <v>171</v>
       </c>
-      <c r="D10" s="26" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="22">
+        <v>46121</v>
+      </c>
+      <c r="J11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" t="s">
         <v>204</v>
       </c>
-      <c r="E10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="G10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H10" s="23">
-        <v>46121</v>
-      </c>
-      <c r="J10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F12" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G12" t="s">
         <v>208</v>
       </c>
-      <c r="C11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="G11" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="23">
-        <v>46121</v>
-      </c>
-      <c r="J11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="B12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E12" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="G12" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="23">
+      <c r="H12" s="22">
         <v>46123</v>
+      </c>
+      <c r="J12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="H13" s="22">
+        <v>46131</v>
+      </c>
+      <c r="J13" t="s">
         <v>171</v>
       </c>
-      <c r="D13" t="s">
-        <v>272</v>
-      </c>
-      <c r="E13" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="H13" s="23">
-        <v>46131</v>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" t="s">
+        <v>315</v>
+      </c>
+      <c r="G14" t="s">
+        <v>316</v>
+      </c>
+      <c r="H14" s="22">
+        <v>46134</v>
+      </c>
+      <c r="J14" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3024,6 +3070,7 @@
     <hyperlink ref="A11" r:id="rId4" xr:uid="{E700B029-EDF2-A045-AF52-4989B15A9704}"/>
     <hyperlink ref="A12" r:id="rId5" xr:uid="{3EA5242D-920D-604D-B0E9-6F5ADEE2537F}"/>
     <hyperlink ref="G13" r:id="rId6" xr:uid="{C04B92CB-055B-1549-9C7C-1350ECD0911C}"/>
+    <hyperlink ref="A14" r:id="rId7" xr:uid="{2C09A1EA-369C-3D42-B213-0F809E3A2ED0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3068,138 +3115,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="36" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="43" t="s">
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="45" t="s">
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="46" t="s">
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="44" t="s">
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
     </row>
     <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="U2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Y2" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AC2" s="6" t="s">
         <v>36</v>
@@ -3213,88 +3260,88 @@
     </row>
     <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="J3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="K3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="O3" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="P3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="R3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="T3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q3" s="10" t="s">
+      <c r="U3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="R3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="T3" s="11" t="s">
+      <c r="Z3" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y3" s="13" t="s">
+      <c r="AA3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="AB3" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="AC3" s="12" t="s">
         <v>46</v>
@@ -3303,7 +3350,7 @@
         <v>46</v>
       </c>
       <c r="AE3" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3330,11 +3377,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" customWidth="1"/>
@@ -3350,82 +3397,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="36" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="43" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="42" t="s">
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
     </row>
     <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>29</v>
@@ -3434,219 +3481,296 @@
         <v>30</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="D3" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="L3" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="N3" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="Q3" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="P3" s="13" t="s">
+      <c r="R3" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="16">
+        <v>230</v>
+      </c>
+      <c r="B4" s="22">
         <v>46129</v>
       </c>
       <c r="C4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>243</v>
+      <c r="F4" s="22">
+        <v>46129</v>
       </c>
       <c r="G4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="P4" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="R4" t="s">
         <v>238</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="P4" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="R4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="16">
+        <v>257</v>
+      </c>
+      <c r="B5" s="22">
         <v>46131</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>267</v>
+      <c r="C5" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="22">
+        <v>46131</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>261</v>
       </c>
       <c r="P5" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q5" s="26" t="s">
-        <v>250</v>
+        <v>171</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="R5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="16">
+        <v>268</v>
+      </c>
+      <c r="B6" s="22">
         <v>46131</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>267</v>
+      <c r="C6" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="22">
+        <v>46131</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>261</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q6" s="26" t="s">
-        <v>250</v>
+        <v>171</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="R6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="35" customFormat="1" ht="128" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" s="38">
+        <v>46134</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="38">
+        <v>46134</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="P7" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>244</v>
       </c>
+      <c r="R7" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
-        <v>214</v>
+      <c r="A9" s="26" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="112" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="16">
+        <v>245</v>
+      </c>
+      <c r="B10" s="22">
         <v>46123</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>232</v>
+        <v>212</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" s="22">
+        <v>46129</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q10" s="26" t="s">
-        <v>250</v>
+        <v>171</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="R10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="22">
+        <v>46131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="38">
+        <v>46134</v>
+      </c>
+      <c r="G11" t="s">
+        <v>304</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="P11" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q11" s="25" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="16">
-        <v>46131</v>
-      </c>
-      <c r="C11" t="s">
-        <v>280</v>
+      <c r="R11" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3672,102 +3796,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E115BE2-B380-C143-9039-D84A47FE0B73}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE01A24-065B-724B-B47C-F54279B090B9}"/>
   <bookViews>
     <workbookView xWindow="1580" yWindow="1680" windowWidth="32480" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="329">
   <si>
     <t>ID</t>
   </si>
@@ -1336,6 +1336,39 @@
   </si>
   <si>
     <t>https://purl.org/cco/ont00000003 (Designative Name)</t>
+  </si>
+  <si>
+    <t>7e7f92583659c80826beebfb533ece7353cb2d34</t>
+  </si>
+  <si>
+    <t>Given Name</t>
+  </si>
+  <si>
+    <t>GivenName</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 11 (GivenName)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See many examples in this row.  Many use label 'first name.'  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 11 (GivenName) </t>
+  </si>
+  <si>
+    <t>skos:altLabel (First Name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A designative Name assigned to a person, usually at birth. </t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — J. Schoening, 2026-04-23</t>
+  </si>
+  <si>
+    <t>J. Schoening, 2026-04-23</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000002</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2069,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2628,7 +2661,72 @@
       <c r="AG8" t="s">
         <v>242</v>
       </c>
+      <c r="AH8" t="s">
+        <v>318</v>
+      </c>
       <c r="AI8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" t="s">
+        <v>324</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="H9" t="s">
+        <v>319</v>
+      </c>
+      <c r="I9" t="s">
+        <v>209</v>
+      </c>
+      <c r="J9" t="s">
+        <v>248</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="L9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC9" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD9" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>275</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI9" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2656,6 +2754,9 @@
     <hyperlink ref="K6" r:id="rId11" xr:uid="{796DC518-82D5-9242-AF71-52FCF4FF1621}"/>
     <hyperlink ref="K8" r:id="rId12" xr:uid="{F2EF0387-CEC0-2D4C-8F4A-37D39AF7718C}"/>
     <hyperlink ref="E8" r:id="rId13" xr:uid="{1ACF9A50-674F-4E41-96DB-E96B0264622A}"/>
+    <hyperlink ref="K9" r:id="rId14" xr:uid="{BEE4D885-0C44-6046-ACAA-3265063D2174}"/>
+    <hyperlink ref="E9" r:id="rId15" xr:uid="{225D3769-6080-0544-8F13-5F98439AE453}"/>
+    <hyperlink ref="A9" r:id="rId16" xr:uid="{81D80342-0CD6-184A-9EF5-6B03692527C7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2666,7 +2767,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3055,6 +3156,32 @@
         <v>46134</v>
       </c>
       <c r="J14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C15" t="s">
+        <v>321</v>
+      </c>
+      <c r="D15" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15" t="s">
+        <v>322</v>
+      </c>
+      <c r="G15" t="s">
+        <v>323</v>
+      </c>
+      <c r="H15" s="22">
+        <v>46134</v>
+      </c>
+      <c r="J15" t="s">
         <v>171</v>
       </c>
     </row>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE01A24-065B-724B-B47C-F54279B090B9}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ED329C-5B9D-5549-8E09-E1235459AECD}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="1680" windowWidth="32480" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1580" yWindow="1680" windowWidth="22520" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="329">
   <si>
     <t>ID</t>
   </si>
@@ -1290,9 +1290,6 @@
     <t>https://purl.org/cco/ont00000649 (Non-Name Identifier)</t>
   </si>
   <si>
-    <t>Proposed</t>
-  </si>
-  <si>
     <t>HL7 FHIR</t>
   </si>
   <si>
@@ -1369,6 +1366,9 @@
   </si>
   <si>
     <t>https://purl.org/cco/ent00000002</t>
+  </si>
+  <si>
+    <t>aa03b7de836e2fee4e4402192cd2111fa541a1e2</t>
   </si>
 </sst>
 </file>
@@ -2617,7 +2617,7 @@
         <v>248</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F8" t="s">
         <v>217</v>
@@ -2635,7 +2635,7 @@
         <v>248</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L8" t="s">
         <v>217</v>
@@ -2662,7 +2662,7 @@
         <v>242</v>
       </c>
       <c r="AH8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AI8" t="s">
         <v>238</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
         <v>209</v>
@@ -2682,16 +2682,16 @@
         <v>248</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G9" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>325</v>
-      </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I9" t="s">
         <v>209</v>
@@ -2700,19 +2700,19 @@
         <v>248</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L9" t="s">
+        <v>323</v>
+      </c>
+      <c r="M9" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="N9" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="N9" s="25" t="s">
+      <c r="AC9" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="AC9" s="25" t="s">
-        <v>327</v>
       </c>
       <c r="AD9" s="25" t="s">
         <v>244</v>
@@ -2726,8 +2726,11 @@
       <c r="AG9" t="s">
         <v>242</v>
       </c>
+      <c r="AH9" t="s">
+        <v>328</v>
+      </c>
       <c r="AI9" t="s">
-        <v>302</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2814,7 +2817,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>53</v>
@@ -2837,7 +2840,7 @@
         <v>182</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>57</v>
@@ -2846,7 +2849,7 @@
         <v>178</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>58</v>
@@ -2892,7 +2895,7 @@
         <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
         <v>179</v>
@@ -3138,19 +3141,19 @@
         <v>290</v>
       </c>
       <c r="C14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" t="s">
         <v>312</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>313</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>314</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>315</v>
-      </c>
-      <c r="G14" t="s">
-        <v>316</v>
       </c>
       <c r="H14" s="22">
         <v>46134</v>
@@ -3161,22 +3164,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" t="s">
         <v>320</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" t="s">
         <v>321</v>
       </c>
-      <c r="D15" t="s">
-        <v>313</v>
-      </c>
-      <c r="E15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>322</v>
-      </c>
-      <c r="G15" t="s">
-        <v>323</v>
       </c>
       <c r="H15" s="22">
         <v>46134</v>
@@ -3789,10 +3792,10 @@
         <v>46134</v>
       </c>
       <c r="C7" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>307</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>308</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>297</v>
@@ -3859,7 +3862,7 @@
         <v>244</v>
       </c>
       <c r="R10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -3873,19 +3876,19 @@
         <v>272</v>
       </c>
       <c r="D11" t="s">
+        <v>303</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>304</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>305</v>
       </c>
       <c r="F11" s="38">
         <v>46134</v>
       </c>
       <c r="G11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H11" s="25" t="s">
         <v>304</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>305</v>
       </c>
       <c r="I11" s="39" t="s">
         <v>295</v>
@@ -3897,7 +3900,7 @@
         <v>244</v>
       </c>
       <c r="R11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ED329C-5B9D-5549-8E09-E1235459AECD}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3184882C-AC60-4D18-9402-3479400D7989}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="1680" windowWidth="22520" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="343">
   <si>
     <t>ID</t>
   </si>
@@ -1370,6 +1370,48 @@
   <si>
     <t>aa03b7de836e2fee4e4402192cd2111fa541a1e2</t>
   </si>
+  <si>
+    <t>A. Sultan Tiwana, 2026-04-28</t>
+  </si>
+  <si>
+    <t>Proposed</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-04-28</t>
+  </si>
+  <si>
+    <t>Family Name</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Surname); skos:altLabel (Last Name)</t>
+  </si>
+  <si>
+    <t>A designative name often referred to as a "last name" in Western contexts or a "surname" in formal contexts.</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000004</t>
+  </si>
+  <si>
+    <t>AlternateName</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Alias)</t>
+  </si>
+  <si>
+    <t>Alternate Name</t>
+  </si>
+  <si>
+    <t>A designative name that is used as a secondary name instead of primary or legal name.</t>
+  </si>
+  <si>
+    <t>A. Sultan Tiwana, 2026-04-29</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-04-29</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000005</t>
+  </si>
 </sst>
 </file>
 
@@ -1378,7 +1420,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1739,7 +1781,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1748,6 +1789,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2069,19 +2111,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.1640625" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.5" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2091,23 +2133,23 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.1640625" customWidth="1"/>
+    <col min="34" max="34" width="16.140625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="21.95" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -2118,45 +2160,45 @@
       <c r="H1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="43" t="s">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
       <c r="AC1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
       <c r="AG1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="42"/>
+      <c r="AH1" s="46"/>
       <c r="AI1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="41.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2263,7 +2305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="72.95" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2349,7 +2391,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="60">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2411,7 +2453,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="90">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2473,7 +2515,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="60">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2538,7 +2580,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="60">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2603,7 +2645,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="105">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2668,7 +2710,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="60">
       <c r="A9" s="34" t="s">
         <v>327</v>
       </c>
@@ -2731,6 +2773,124 @@
       </c>
       <c r="AI9" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" ht="75">
+      <c r="A10" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="F10" t="s">
+        <v>333</v>
+      </c>
+      <c r="G10" t="s">
+        <v>334</v>
+      </c>
+      <c r="H10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I10" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10" t="s">
+        <v>248</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="L10" t="s">
+        <v>333</v>
+      </c>
+      <c r="M10" t="s">
+        <v>334</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC10" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="AD10" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" ht="75">
+      <c r="A11" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I11" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" t="s">
+        <v>248</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="L11" t="s">
+        <v>337</v>
+      </c>
+      <c r="M11" t="s">
+        <v>339</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="AC11" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD11" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -2760,6 +2920,12 @@
     <hyperlink ref="K9" r:id="rId14" xr:uid="{BEE4D885-0C44-6046-ACAA-3265063D2174}"/>
     <hyperlink ref="E9" r:id="rId15" xr:uid="{225D3769-6080-0544-8F13-5F98439AE453}"/>
     <hyperlink ref="A9" r:id="rId16" xr:uid="{81D80342-0CD6-184A-9EF5-6B03692527C7}"/>
+    <hyperlink ref="E10" r:id="rId17" xr:uid="{FE238C6D-6493-489B-8372-68F519A30A7E}"/>
+    <hyperlink ref="K10" r:id="rId18" xr:uid="{6D3F89FA-BD51-4F8D-B879-7FC04539B40F}"/>
+    <hyperlink ref="A10" r:id="rId19" xr:uid="{56707C81-2279-4391-8851-764A876CA52A}"/>
+    <hyperlink ref="E11" r:id="rId20" xr:uid="{A3830EF3-62BA-4D9B-AB67-D2DB92E39CD2}"/>
+    <hyperlink ref="K11" r:id="rId21" xr:uid="{69C5A3AE-00D8-4CE0-9258-90B2C623F68E}"/>
+    <hyperlink ref="A11" r:id="rId22" xr:uid="{8B635C41-7A6F-41D4-A634-D3781E044C3D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2771,36 +2937,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.1640625" customWidth="1"/>
+    <col min="6" max="6" width="232.140625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
       <c r="D1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-    </row>
-    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+    </row>
+    <row r="2" spans="1:10" ht="44.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -2832,7 +2998,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="90" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -2861,7 +3027,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -2887,7 +3053,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -2913,7 +3079,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="18">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -2939,7 +3105,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -2965,7 +3131,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -2994,7 +3160,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16.5">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3023,7 +3189,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="14.1" customHeight="1">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3049,7 +3215,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3078,7 +3244,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3107,7 +3273,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3133,7 +3299,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3162,7 +3328,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
         <v>319</v>
       </c>
@@ -3213,7 +3379,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3244,56 +3410,56 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="21.95" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
       <c r="F1" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
       <c r="J1" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
       <c r="O1" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
       <c r="T1" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
       <c r="Y1" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="42"/>
+      <c r="Z1" s="46"/>
       <c r="AA1" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="42"/>
+      <c r="AB1" s="46"/>
       <c r="AC1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-    </row>
-    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+    </row>
+    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -3388,7 +3554,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="72" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -3504,9 +3670,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -3514,51 +3680,51 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="21.95" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
       <c r="D1" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
       <c r="G1" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
       <c r="J1" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
       <c r="P1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-    </row>
-    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+    </row>
+    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -3614,7 +3780,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="95.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -3670,7 +3836,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="105">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -3708,7 +3874,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="165">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -3746,7 +3912,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="165">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -3784,7 +3950,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="35" customFormat="1" ht="128" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="35" customFormat="1" ht="135">
       <c r="A7" s="35" t="s">
         <v>289</v>
       </c>
@@ -3822,12 +3988,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="135">
       <c r="A10" t="s">
         <v>245</v>
       </c>
@@ -3865,7 +4031,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="75">
       <c r="A11" t="s">
         <v>271</v>
       </c>
@@ -3919,107 +4085,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="27.95" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="27.95" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="36" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="27.95" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="36" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="27.95" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="90.95" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="27.95" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="36" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="27.95" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="90.95" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="27.95" customHeight="1">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="63" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="27.95" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="63" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="27.95" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="63" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="27.95" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{1F7C4A89-5424-3240-8BA9-F49F8277699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3184882C-AC60-4D18-9402-3479400D7989}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C1A02A0-8937-6341-8994-E26824C11D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20740" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="344">
   <si>
     <t>ID</t>
   </si>
@@ -1412,6 +1412,9 @@
   <si>
     <t>https://purl.org/cco/ent00000005</t>
   </si>
+  <si>
+    <t>4747a27fa752f65269e2490c8e90839937362847</t>
+  </si>
 </sst>
 </file>
 
@@ -1420,7 +1423,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2112,18 +2115,18 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.42578125" customWidth="1"/>
+    <col min="12" max="12" width="37.5" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2133,23 +2136,23 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.140625" customWidth="1"/>
+    <col min="34" max="34" width="16.1640625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="21.95" customHeight="1">
+    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41.1" customHeight="1">
+    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2305,7 +2308,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="72.95" customHeight="1">
+    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2391,7 +2394,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="60">
+    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2453,7 +2456,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="90">
+    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2515,7 +2518,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="60">
+    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2580,7 +2583,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="60">
+    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="105">
+    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="60">
+    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
         <v>327</v>
       </c>
@@ -2775,7 +2778,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="75">
+    <row r="10" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>335</v>
       </c>
@@ -2834,7 +2837,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="75">
+    <row r="11" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>342</v>
       </c>
@@ -2889,8 +2892,11 @@
       <c r="AG11" t="s">
         <v>242</v>
       </c>
+      <c r="AH11" t="s">
+        <v>343</v>
+      </c>
       <c r="AI11" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2937,21 +2943,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.140625" customWidth="1"/>
+    <col min="6" max="6" width="232.1640625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>47</v>
       </c>
@@ -2966,7 +2972,7 @@
       <c r="H1" s="46"/>
       <c r="I1" s="46"/>
     </row>
-    <row r="2" spans="1:10" ht="44.1" customHeight="1">
+    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -2998,7 +3004,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1">
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -3027,7 +3033,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -3053,7 +3059,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -3079,7 +3085,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -3105,7 +3111,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -3160,7 +3166,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5">
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3189,7 +3195,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.1" customHeight="1">
+    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1">
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3244,7 +3250,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3273,7 +3279,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3299,7 +3305,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3328,7 +3334,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>319</v>
       </c>
@@ -3379,7 +3385,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3410,7 +3416,7 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="21.95" customHeight="1">
+    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>61</v>
       </c>
@@ -3459,7 +3465,7 @@
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
     </row>
-    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1">
+    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -3670,9 +3676,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -3680,19 +3686,19 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21.95" customHeight="1">
+    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>116</v>
       </c>
@@ -3724,7 +3730,7 @@
       <c r="Q1" s="46"/>
       <c r="R1" s="46"/>
     </row>
-    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
+    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95.1" customHeight="1">
+    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -3836,7 +3842,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="105">
+    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -3874,7 +3880,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="165">
+    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -3912,7 +3918,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="165">
+    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -3950,7 +3956,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="35" customFormat="1" ht="135">
+    <row r="7" spans="1:18" s="35" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
         <v>289</v>
       </c>
@@ -3988,12 +3994,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="135">
+    <row r="10" spans="1:18" ht="128" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>245</v>
       </c>
@@ -4031,7 +4037,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="75">
+    <row r="11" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>271</v>
       </c>
@@ -4085,107 +4091,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.95" customHeight="1">
+    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="27.95" customHeight="1">
+    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1">
+    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="27.95" customHeight="1">
+    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1">
+    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="27.95" customHeight="1">
+    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="90.95" customHeight="1">
+    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="27.95" customHeight="1">
+    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1">
+    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="27.95" customHeight="1">
+    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="90.95" customHeight="1">
+    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="27.95" customHeight="1">
+    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1">
+    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27.95" customHeight="1">
+    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1">
+    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27.95" customHeight="1">
+    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1">
+    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="27.95" customHeight="1">
+    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1">
+    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C1A02A0-8937-6341-8994-E26824C11D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED9CB8-EAD5-454D-A180-8FCC1F838673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20740" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10900" yWindow="600" windowWidth="29400" windowHeight="16660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="354">
   <si>
     <t>ID</t>
   </si>
@@ -1414,6 +1414,36 @@
   </si>
   <si>
     <t>4747a27fa752f65269e2490c8e90839937362847</t>
+  </si>
+  <si>
+    <t>AD-007</t>
+  </si>
+  <si>
+    <t>How to use P3195.1.1 Cyber Ontology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are many categories of identifiers for a person.  It would be too much work at this early stage to research all these categories to develop a comprehensive solution.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current drafts of IEEE P3195.1.1 Cyber Ontology incorporate all or parts of CCO rather than importing it, so Cyber Ontology technically does not conform to CCO.  If an application contology tries to import Cyber Ontology, it wll get classes found in both Cyber and CCO and can't proceed.  As such, we will draw needed excerpts from Cyber Onology, give full copyright, and cite the Target Ontology as a CCO-conforming version of IEEE P3195.1.1.   If never feasible to move to Cyber Ontology, this is valid use of open source content. </t>
+  </si>
+  <si>
+    <t>Take excerpts from IEEE P3195.1.1 Cyber Ontology and place in Staging Ontology, when needed by application ontologies.  Within each entity drawn from Cyber Ontology, include 'dcterms:rightsHolder "CUBRC, Inc." '  Mint new CCO-Domains IRIs, which can later be redirected to Cyber Ontology when feasible.</t>
+  </si>
+  <si>
+    <t>AD-008</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — J. Schoening, 2026-04-30</t>
+  </si>
+  <si>
+    <t>How to provide addresses, include US Postal addresses</t>
+  </si>
+  <si>
+    <t>Create an Address Ontology and within it, create the entities for US Post Addresses.  Enhance when we have broader demand and more contributors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are various types of addresses used for various Use Cases, including address schemes for almost every country in the world, delivery services, emergency response, tax purposes, water, etc.  This is too much to try to cover at this time, so best to create a new domain ontology (addresses are important to the Person, but don't belong in Person Ontology), and cover only specific requirements, which for now is US Postal addresses. </t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1769,7 +1799,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1781,7 +1810,20 @@
     <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1792,22 +1834,15 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2153,51 +2188,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="27"/>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="42" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="44" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="47" t="s">
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="41" t="s">
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="41" t="s">
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="43" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2456,7 +2491,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2596,7 +2631,7 @@
       <c r="D7" t="s">
         <v>248</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="36" t="s">
         <v>301</v>
       </c>
       <c r="F7" t="s">
@@ -2614,7 +2649,7 @@
       <c r="J7" t="s">
         <v>248</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="36" t="s">
         <v>301</v>
       </c>
       <c r="L7" t="s">
@@ -2958,19 +2993,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3292,7 +3327,7 @@
       <c r="E13" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="35" t="s">
         <v>265</v>
       </c>
       <c r="G13" s="17" t="s">
@@ -3417,53 +3452,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="41" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="50" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="51" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="47" t="s">
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="41" t="s">
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="49" t="s">
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
     </row>
     <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3675,7 +3710,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -3699,36 +3734,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="48" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="50" t="s">
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="51" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="47" t="s">
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
     </row>
     <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3802,7 +3837,7 @@
       <c r="E3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="39" t="s">
         <v>136</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -3956,122 +3991,195 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="35" customFormat="1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:18" s="51" customFormat="1" ht="128" x14ac:dyDescent="0.2">
+      <c r="A7" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="52">
         <v>46134</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="52">
         <v>46134</v>
       </c>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="51" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+    <row r="8" spans="1:18" ht="160" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="52">
+        <v>46142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="F8" s="52">
+        <v>46142</v>
+      </c>
+      <c r="G8" t="s">
+        <v>348</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="I8" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="R8" s="54" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B9" s="52">
+        <v>46142</v>
+      </c>
+      <c r="C9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" s="52">
+        <v>46142</v>
+      </c>
+      <c r="G9" t="s">
+        <v>352</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q9" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="R9" s="54" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="128" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="13" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>245</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B13" s="22">
         <v>46123</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C13" t="s">
         <v>212</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D13" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E13" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F13" s="22">
         <v>46129</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G13" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H13" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I13" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P13" t="s">
         <v>171</v>
       </c>
-      <c r="Q10" s="25" t="s">
+      <c r="Q13" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R13" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="14" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>271</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B14" s="22">
         <v>46131</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D14" t="s">
         <v>303</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E14" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F14" s="37">
         <v>46134</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G14" t="s">
         <v>303</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="I11" s="39" t="s">
+      <c r="H14" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="I14" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P14" t="s">
         <v>171</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="Q14" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R14" t="s">
         <v>305</v>
       </c>
     </row>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED9CB8-EAD5-454D-A180-8FCC1F838673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{57642275-3734-42A7-AB65-B6394FB0BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EA2F383-DE82-4D84-A360-082BA0CCB0A2}"/>
   <bookViews>
-    <workbookView xWindow="10900" yWindow="600" windowWidth="29400" windowHeight="16660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="379">
   <si>
     <t>ID</t>
   </si>
@@ -1329,9 +1329,6 @@
     <t xml:space="preserve">See many examples in this row.  Many use label 'name' for full name.  </t>
   </si>
   <si>
-    <t xml:space="preserve">See links in row 10 (FullName) </t>
-  </si>
-  <si>
     <t>https://purl.org/cco/ont00000003 (Designative Name)</t>
   </si>
   <si>
@@ -1350,9 +1347,6 @@
     <t xml:space="preserve">See many examples in this row.  Many use label 'first name.'  </t>
   </si>
   <si>
-    <t xml:space="preserve">See links in row 11 (GivenName) </t>
-  </si>
-  <si>
     <t>skos:altLabel (First Name)</t>
   </si>
   <si>
@@ -1392,9 +1386,6 @@
     <t>https://purl.org/cco/ent00000004</t>
   </si>
   <si>
-    <t>AlternateName</t>
-  </si>
-  <si>
     <t>skos:altLabel (Alias)</t>
   </si>
   <si>
@@ -1404,18 +1395,9 @@
     <t>A designative name that is used as a secondary name instead of primary or legal name.</t>
   </si>
   <si>
-    <t>A. Sultan Tiwana, 2026-04-29</t>
-  </si>
-  <si>
-    <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-04-29</t>
-  </si>
-  <si>
     <t>https://purl.org/cco/ent00000005</t>
   </si>
   <si>
-    <t>4747a27fa752f65269e2490c8e90839937362847</t>
-  </si>
-  <si>
     <t>AD-007</t>
   </si>
   <si>
@@ -1444,6 +1426,99 @@
   </si>
   <si>
     <t xml:space="preserve">There are various types of addresses used for various Use Cases, including address schemes for almost every country in the world, delivery services, emergency response, tax purposes, water, etc.  This is too much to try to cover at this time, so best to create a new domain ontology (addresses are important to the Person, but don't belong in Person Ontology), and cover only specific requirements, which for now is US Postal addresses. </t>
+  </si>
+  <si>
+    <t>Additional Name</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000003</t>
+  </si>
+  <si>
+    <t>A. Sultan Tiwana, 2026-05-01</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-05-01</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000006</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Surname2</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000058</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000057</t>
+  </si>
+  <si>
+    <t>A designative name that refers as an extra identifier and supplements a primary name.</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Middle Name)</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Name Suffix); skos:example ("Sr.". "Ret.". "PhD")</t>
+  </si>
+  <si>
+    <t>A designative name added after the person's full name to add more information(professional, generational or academic).</t>
+  </si>
+  <si>
+    <t>A designative name added before the person's given name to add more information(professional, marital status or religious).</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Name Prefix); skos:altLabel (Honorific); skos:example ("Mr.". "Dr.". "Prof.")</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Second Family Name); skos:altLabel (Second Surname); skos:altLabel (Maternal Surname)</t>
+  </si>
+  <si>
+    <t>A designative name that represents the second family name . commonly a maternal surname.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 8(Full Name) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 9 (Given Name) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 10(Family Name) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 11(Alternate Name) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 12(Additional Name) </t>
+  </si>
+  <si>
+    <t>See links in row 13(Suffix)</t>
+  </si>
+  <si>
+    <t>See links in row 14(Title)</t>
+  </si>
+  <si>
+    <t>See links in row 15(Surname2)</t>
+  </si>
+  <si>
+    <t>A. Sultan Tiwana</t>
+  </si>
+  <si>
+    <t>0f6705c9cc34aa9cb1b154f6379f4155f974285e</t>
+  </si>
+  <si>
+    <t>A designative name added after the person's full name to add more information (professional, generational or academic).</t>
+  </si>
+  <si>
+    <t>A designative name added before the person's given name to add more information (professional, marital status or religious).</t>
+  </si>
+  <si>
+    <t>A designative name that represents the second family name, commonly a maternal surname.</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1528,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1713,7 +1788,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1810,20 +1885,7 @@
     <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1834,15 +1896,22 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2149,19 +2218,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AI15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.1640625" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.5" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2171,72 +2240,72 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.1640625" customWidth="1"/>
+    <col min="34" max="34" width="16.140625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:35" ht="21.95" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="27"/>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="46" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="48" t="s">
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="42" t="s">
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
+      <c r="AC1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="43" t="s">
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="43" t="s">
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="40" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="41.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2343,7 +2412,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="72.95" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2429,7 +2498,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="60">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2491,7 +2560,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="90">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2553,7 +2622,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="60">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2618,7 +2687,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="60">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2683,7 +2752,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="105">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2697,7 +2766,7 @@
         <v>248</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8" t="s">
         <v>217</v>
@@ -2715,7 +2784,7 @@
         <v>248</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L8" t="s">
         <v>217</v>
@@ -2742,18 +2811,18 @@
         <v>242</v>
       </c>
       <c r="AH8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AI8" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="60">
       <c r="A9" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
         <v>209</v>
@@ -2762,16 +2831,16 @@
         <v>248</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I9" t="s">
         <v>209</v>
@@ -2780,19 +2849,19 @@
         <v>248</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L9" t="s">
+        <v>321</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="N9" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="AC9" s="25" t="s">
         <v>324</v>
-      </c>
-      <c r="N9" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="AC9" s="25" t="s">
-        <v>326</v>
       </c>
       <c r="AD9" s="25" t="s">
         <v>244</v>
@@ -2807,18 +2876,18 @@
         <v>242</v>
       </c>
       <c r="AH9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AI9" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="75">
       <c r="A10" s="17" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C10" t="s">
         <v>209</v>
@@ -2827,16 +2896,16 @@
         <v>248</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I10" t="s">
         <v>209</v>
@@ -2845,19 +2914,19 @@
         <v>248</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AC10" s="25" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AD10" s="25" t="s">
         <v>244</v>
@@ -2868,16 +2937,19 @@
       <c r="AG10" t="s">
         <v>242</v>
       </c>
+      <c r="AH10" t="s">
+        <v>375</v>
+      </c>
       <c r="AI10" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" ht="75">
       <c r="A11" s="17" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C11" t="s">
         <v>209</v>
@@ -2886,16 +2958,16 @@
         <v>248</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I11" t="s">
         <v>209</v>
@@ -2904,19 +2976,19 @@
         <v>248</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AD11" s="25" t="s">
         <v>244</v>
@@ -2927,11 +2999,244 @@
       <c r="AG11" t="s">
         <v>242</v>
       </c>
-      <c r="AH11" t="s">
-        <v>343</v>
-      </c>
       <c r="AI11" t="s">
-        <v>238</v>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="75">
+      <c r="A12" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12" t="s">
+        <v>359</v>
+      </c>
+      <c r="G12" t="s">
+        <v>358</v>
+      </c>
+      <c r="H12" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" t="s">
+        <v>209</v>
+      </c>
+      <c r="J12" t="s">
+        <v>248</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L12" t="s">
+        <v>359</v>
+      </c>
+      <c r="M12" t="s">
+        <v>358</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="AC12" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD12" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="75">
+      <c r="A13" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F13" t="s">
+        <v>360</v>
+      </c>
+      <c r="G13" t="s">
+        <v>376</v>
+      </c>
+      <c r="H13" t="s">
+        <v>353</v>
+      </c>
+      <c r="I13" t="s">
+        <v>209</v>
+      </c>
+      <c r="J13" t="s">
+        <v>248</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L13" t="s">
+        <v>360</v>
+      </c>
+      <c r="M13" t="s">
+        <v>361</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="AC13" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD13" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="75">
+      <c r="A14" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="B14" t="s">
+        <v>354</v>
+      </c>
+      <c r="C14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14" t="s">
+        <v>363</v>
+      </c>
+      <c r="G14" t="s">
+        <v>377</v>
+      </c>
+      <c r="H14" t="s">
+        <v>354</v>
+      </c>
+      <c r="I14" t="s">
+        <v>209</v>
+      </c>
+      <c r="J14" t="s">
+        <v>248</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L14" t="s">
+        <v>363</v>
+      </c>
+      <c r="M14" t="s">
+        <v>362</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="AC14" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD14" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="75">
+      <c r="A15" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" t="s">
+        <v>364</v>
+      </c>
+      <c r="G15" t="s">
+        <v>378</v>
+      </c>
+      <c r="H15" t="s">
+        <v>355</v>
+      </c>
+      <c r="I15" t="s">
+        <v>209</v>
+      </c>
+      <c r="J15" t="s">
+        <v>248</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L15" t="s">
+        <v>364</v>
+      </c>
+      <c r="M15" t="s">
+        <v>365</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="AC15" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD15" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -2967,8 +3272,21 @@
     <hyperlink ref="E11" r:id="rId20" xr:uid="{A3830EF3-62BA-4D9B-AB67-D2DB92E39CD2}"/>
     <hyperlink ref="K11" r:id="rId21" xr:uid="{69C5A3AE-00D8-4CE0-9258-90B2C623F68E}"/>
     <hyperlink ref="A11" r:id="rId22" xr:uid="{8B635C41-7A6F-41D4-A634-D3781E044C3D}"/>
+    <hyperlink ref="A12" r:id="rId23" xr:uid="{045280ED-D616-4D25-BF9F-F0DA4BBBDB19}"/>
+    <hyperlink ref="E12" r:id="rId24" xr:uid="{3E96FC7D-2F8B-4AAF-B326-67C33152CC4B}"/>
+    <hyperlink ref="K12" r:id="rId25" xr:uid="{596A7E46-AFFA-4D75-B074-9136F4E4319B}"/>
+    <hyperlink ref="A13" r:id="rId26" xr:uid="{C7F755D2-2734-4B0E-A0D6-6570E652825D}"/>
+    <hyperlink ref="E13" r:id="rId27" xr:uid="{F64654AC-FEF5-4FC3-9565-6E36307A0479}"/>
+    <hyperlink ref="K13" r:id="rId28" xr:uid="{3AD0D554-372A-44AC-910D-5E49349EE3EB}"/>
+    <hyperlink ref="A14" r:id="rId29" xr:uid="{58B1E345-E12E-40D6-A5C9-212F8D76324F}"/>
+    <hyperlink ref="E14" r:id="rId30" xr:uid="{C541F9A3-810A-43AE-BA15-A5E76881CB46}"/>
+    <hyperlink ref="K14" r:id="rId31" xr:uid="{CC2597AE-A81F-4994-BF5C-C76C45431A06}"/>
+    <hyperlink ref="A15" r:id="rId32" xr:uid="{BDEDD28F-25E0-4FEC-9F29-77B2F0701D15}"/>
+    <hyperlink ref="E15" r:id="rId33" xr:uid="{6EA9E125-DA9A-4D27-A615-CFBED67ACCB2}"/>
+    <hyperlink ref="K15" r:id="rId34" xr:uid="{C4972275-C907-4488-902A-0F1A94D8A3F2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>
 
@@ -2977,37 +3295,37 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.1640625" customWidth="1"/>
+    <col min="6" max="6" width="232.140625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="43" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+    </row>
+    <row r="2" spans="1:10" ht="44.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -3039,7 +3357,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="90" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -3068,7 +3386,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -3094,7 +3412,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -3120,7 +3438,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="18">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -3146,7 +3464,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -3172,7 +3490,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -3201,7 +3519,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16.5">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3230,7 +3548,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="14.1" customHeight="1">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3256,7 +3574,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3285,7 +3603,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3314,7 +3632,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3340,7 +3658,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3360,7 +3678,7 @@
         <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="H14" s="22">
         <v>46134</v>
@@ -3369,12 +3687,12 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
+        <v>318</v>
+      </c>
+      <c r="C15" t="s">
         <v>319</v>
-      </c>
-      <c r="C15" t="s">
-        <v>320</v>
       </c>
       <c r="D15" t="s">
         <v>312</v>
@@ -3383,16 +3701,82 @@
         <v>313</v>
       </c>
       <c r="F15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G15" t="s">
-        <v>322</v>
+        <v>367</v>
       </c>
       <c r="H15" s="22">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="J15" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="G16" t="s">
+        <v>368</v>
+      </c>
+      <c r="H16" s="22">
+        <v>46140</v>
+      </c>
+      <c r="J16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10">
+      <c r="G17" t="s">
+        <v>369</v>
+      </c>
+      <c r="H17" s="22">
+        <v>46141</v>
+      </c>
+      <c r="J17" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10">
+      <c r="G18" t="s">
+        <v>370</v>
+      </c>
+      <c r="H18" s="22">
+        <v>46143</v>
+      </c>
+      <c r="J18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10">
+      <c r="G19" t="s">
+        <v>371</v>
+      </c>
+      <c r="H19" s="22">
+        <v>46143</v>
+      </c>
+      <c r="J19" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10">
+      <c r="G20" t="s">
+        <v>372</v>
+      </c>
+      <c r="H20" s="22">
+        <v>46143</v>
+      </c>
+      <c r="J20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10">
+      <c r="G21" t="s">
+        <v>373</v>
+      </c>
+      <c r="H21" s="22">
+        <v>46143</v>
+      </c>
+      <c r="J21" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3420,7 +3804,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3451,56 +3835,56 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:31" ht="21.95" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="43" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="45" t="s">
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="40" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="44" t="s">
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="42" t="s">
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="43" t="s">
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="50" t="s">
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-    </row>
-    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+    </row>
+    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -3595,7 +3979,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="72" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -3711,9 +4095,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -3721,51 +4105,51 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:18" ht="21.95" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="43" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="45" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="40" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="44" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-    </row>
-    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+    </row>
+    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -3821,7 +4205,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="95.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -3877,7 +4261,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="105">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -3915,7 +4299,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="165">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -3953,7 +4337,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="165">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -3991,123 +4375,123 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="51" customFormat="1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
+    <row r="7" spans="1:18" ht="135">
+      <c r="A7" t="s">
         <v>289</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="22">
         <v>46134</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="22">
         <v>46134</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="I7" s="53" t="s">
+      <c r="I7" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="P7" s="51" t="s">
+      <c r="P7" t="s">
         <v>171</v>
       </c>
-      <c r="Q7" s="53" t="s">
+      <c r="Q7" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="R7" s="51" t="s">
+      <c r="R7" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="160" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="180">
       <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="22">
+        <v>46142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="22">
+        <v>46142</v>
+      </c>
+      <c r="G8" t="s">
+        <v>342</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="I8" s="25" t="s">
         <v>344</v>
       </c>
-      <c r="B8" s="52">
+      <c r="P8" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="R8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="150">
+      <c r="A9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B9" s="22">
         <v>46142</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>345</v>
       </c>
-      <c r="D8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E8" s="25" t="s">
+      <c r="D9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E9" s="25" t="s">
         <v>347</v>
       </c>
-      <c r="F8" s="52">
+      <c r="F9" s="22">
         <v>46142</v>
       </c>
-      <c r="G8" t="s">
-        <v>348</v>
-      </c>
-      <c r="H8" s="25" t="s">
+      <c r="G9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>347</v>
       </c>
-      <c r="I8" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="P8" s="51" t="s">
+      <c r="P9" t="s">
         <v>171</v>
       </c>
-      <c r="Q8" s="53" t="s">
+      <c r="Q9" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="R8" s="54" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="144" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>349</v>
-      </c>
-      <c r="B9" s="52">
-        <v>46142</v>
-      </c>
-      <c r="C9" t="s">
-        <v>351</v>
-      </c>
-      <c r="D9" t="s">
-        <v>352</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="F9" s="52">
-        <v>46142</v>
-      </c>
-      <c r="G9" t="s">
-        <v>352</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q9" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="R9" s="54" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="135">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -4145,7 +4529,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="75">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -4168,7 +4552,7 @@
         <v>303</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I14" s="38" t="s">
         <v>295</v>
@@ -4199,107 +4583,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="27.95" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="27.95" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="36" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="27.95" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="36" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="27.95" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="90.95" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="27.95" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="36" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="27.95" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="90.95" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="27.95" customHeight="1">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="63" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="27.95" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="63" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="27.95" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="63" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="27.95" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{57642275-3734-42A7-AB65-B6394FB0BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EA2F383-DE82-4D84-A360-082BA0CCB0A2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89597682-6B83-4647-B1E2-65003E461C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="48320" windowHeight="23040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -1520,6 +1520,9 @@
   <si>
     <t>A designative name that represents the second family name, commonly a maternal surname.</t>
   </si>
+  <si>
+    <t>34f1f67341ae4af03d91607b63075593fdb55f71</t>
+  </si>
 </sst>
 </file>
 
@@ -1528,7 +1531,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2219,18 +2222,18 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AI15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.42578125" customWidth="1"/>
+    <col min="12" max="12" width="37.5" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2240,23 +2243,23 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.140625" customWidth="1"/>
+    <col min="34" max="34" width="16.1640625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="21.95" customHeight="1">
+    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -2305,7 +2308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41.1" customHeight="1">
+    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2412,7 +2415,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="72.95" customHeight="1">
+    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="60">
+    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="90">
+    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="60">
+    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2687,7 +2690,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="60">
+    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="105">
+    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2817,7 +2820,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="60">
+    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
         <v>325</v>
       </c>
@@ -2882,7 +2885,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="75">
+    <row r="10" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>333</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="75">
+    <row r="11" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>352</v>
       </c>
@@ -2999,11 +3002,14 @@
       <c r="AG11" t="s">
         <v>242</v>
       </c>
+      <c r="AH11" t="s">
+        <v>379</v>
+      </c>
       <c r="AI11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>349</v>
       </c>
@@ -3058,11 +3064,14 @@
       <c r="AG12" t="s">
         <v>242</v>
       </c>
+      <c r="AH12" t="s">
+        <v>379</v>
+      </c>
       <c r="AI12" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>337</v>
       </c>
@@ -3117,11 +3126,14 @@
       <c r="AG13" t="s">
         <v>242</v>
       </c>
+      <c r="AH13" t="s">
+        <v>379</v>
+      </c>
       <c r="AI13" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>357</v>
       </c>
@@ -3176,11 +3188,14 @@
       <c r="AG14" t="s">
         <v>242</v>
       </c>
+      <c r="AH14" t="s">
+        <v>379</v>
+      </c>
       <c r="AI14" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>356</v>
       </c>
@@ -3235,8 +3250,11 @@
       <c r="AG15" t="s">
         <v>242</v>
       </c>
+      <c r="AH15" t="s">
+        <v>379</v>
+      </c>
       <c r="AI15" t="s">
-        <v>328</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3296,21 +3314,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.140625" customWidth="1"/>
+    <col min="6" max="6" width="232.1640625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
@@ -3325,7 +3343,7 @@
       <c r="H1" s="45"/>
       <c r="I1" s="45"/>
     </row>
-    <row r="2" spans="1:10" ht="44.1" customHeight="1">
+    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -3357,7 +3375,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1">
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -3386,7 +3404,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -3412,7 +3430,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -3438,7 +3456,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -3464,7 +3482,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -3490,7 +3508,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -3519,7 +3537,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5">
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3548,7 +3566,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.1" customHeight="1">
+    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3574,7 +3592,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1">
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3603,7 +3621,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3632,7 +3650,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3658,7 +3676,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3687,7 +3705,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>318</v>
       </c>
@@ -3713,7 +3731,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="G16" t="s">
         <v>368</v>
       </c>
@@ -3724,7 +3742,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="17" spans="7:10">
+    <row r="17" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G17" t="s">
         <v>369</v>
       </c>
@@ -3735,7 +3753,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="18" spans="7:10">
+    <row r="18" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
         <v>370</v>
       </c>
@@ -3746,7 +3764,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="19" spans="7:10">
+    <row r="19" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G19" t="s">
         <v>371</v>
       </c>
@@ -3757,7 +3775,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="7:10">
+    <row r="20" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G20" t="s">
         <v>372</v>
       </c>
@@ -3768,7 +3786,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="21" spans="7:10">
+    <row r="21" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G21" t="s">
         <v>373</v>
       </c>
@@ -3804,7 +3822,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3835,7 +3853,7 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="21.95" customHeight="1">
+    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>61</v>
       </c>
@@ -3884,7 +3902,7 @@
       <c r="AD1" s="45"/>
       <c r="AE1" s="45"/>
     </row>
-    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -3979,7 +3997,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1">
+    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -4095,9 +4113,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -4105,19 +4123,19 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21.95" customHeight="1">
+    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>116</v>
       </c>
@@ -4149,7 +4167,7 @@
       <c r="Q1" s="45"/>
       <c r="R1" s="45"/>
     </row>
-    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
+    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -4205,7 +4223,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95.1" customHeight="1">
+    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -4261,7 +4279,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="105">
+    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -4299,7 +4317,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="165">
+    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -4337,7 +4355,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="165">
+    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -4375,7 +4393,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="135">
+    <row r="7" spans="1:18" ht="128" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -4413,7 +4431,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="180">
+    <row r="8" spans="1:18" ht="160" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>338</v>
       </c>
@@ -4451,7 +4469,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="150">
+    <row r="9" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>343</v>
       </c>
@@ -4486,12 +4504,12 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="135">
+    <row r="13" spans="1:18" ht="128" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -4529,7 +4547,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75">
+    <row r="14" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -4583,107 +4601,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.95" customHeight="1">
+    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="27.95" customHeight="1">
+    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1">
+    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="27.95" customHeight="1">
+    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1">
+    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="27.95" customHeight="1">
+    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="90.95" customHeight="1">
+    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="27.95" customHeight="1">
+    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1">
+    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="27.95" customHeight="1">
+    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="90.95" customHeight="1">
+    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="27.95" customHeight="1">
+    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1">
+    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27.95" customHeight="1">
+    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1">
+    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27.95" customHeight="1">
+    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1">
+    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="27.95" customHeight="1">
+    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1">
+    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89597682-6B83-4647-B1E2-65003E461C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{57642275-3734-42A7-AB65-B6394FB0BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A39A6A4B-817E-410C-BDBF-A41C11F49C32}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="48320" windowHeight="23040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="408">
   <si>
     <t>ID</t>
   </si>
@@ -1497,9 +1497,6 @@
     <t xml:space="preserve">See links in row 12(Additional Name) </t>
   </si>
   <si>
-    <t>See links in row 13(Suffix)</t>
-  </si>
-  <si>
     <t>See links in row 14(Title)</t>
   </si>
   <si>
@@ -1521,7 +1518,94 @@
     <t>A designative name that represents the second family name, commonly a maternal surname.</t>
   </si>
   <si>
-    <t>34f1f67341ae4af03d91607b63075593fdb55f71</t>
+    <t>https://purl.org/cco/ent00000023</t>
+  </si>
+  <si>
+    <t>Telephone Number</t>
+  </si>
+  <si>
+    <t>StagingOntology</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a paticular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Phone Number)</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-05-05</t>
+  </si>
+  <si>
+    <t>A. Sultan Tiwana, 2026-05-05</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ont00000958 (Information Content Entity)</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>skos:altLabel (Electronic Mail Address); skos:altLabel (Email ID)</t>
+  </si>
+  <si>
+    <t>FamilyName</t>
+  </si>
+  <si>
+    <t>AlternateName</t>
+  </si>
+  <si>
+    <t>AdditionalName</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 9 (FamilyName)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See many examples in this row.  Many use label 'last name.'  </t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 13 (AlternateName)</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 15 (AdditionalName)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See many examples in this row.  Many use label 'middle name.'  </t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 168 (Suffix)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See links in row 13(Suffix) </t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 16 (Salutation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See many examples in this row.  Many use label 'honorific prefix.'  </t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000024</t>
+  </si>
+  <si>
+    <t>TelephoneNumber</t>
+  </si>
+  <si>
+    <t>EmailAddress</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 26 (telephonenumber)</t>
+  </si>
+  <si>
+    <t>Candidate Terms Row 29 (emailAddress)</t>
+  </si>
+  <si>
+    <t>See links in row 16(Telephone Number)</t>
+  </si>
+  <si>
+    <t>See links in row 17(Email Address)</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consists of a unique address assigned to a person, enabling the sending and receiving of electronic messages through a mail server over the network.</t>
   </si>
 </sst>
 </file>
@@ -1531,7 +1615,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1933,6 +2017,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2221,19 +2309,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AI17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.1640625" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.5" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2243,23 +2331,23 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.1640625" customWidth="1"/>
+    <col min="34" max="34" width="16.140625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="21.95" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -2308,7 +2396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="41.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2415,7 +2503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="72.95" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2501,7 +2589,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="60">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2563,7 +2651,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="90">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2625,7 +2713,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="60">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2690,7 +2778,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="60">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2755,7 +2843,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="105">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2820,7 +2908,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="60">
       <c r="A9" s="34" t="s">
         <v>325</v>
       </c>
@@ -2885,7 +2973,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="75">
       <c r="A10" s="17" t="s">
         <v>333</v>
       </c>
@@ -2941,13 +3029,13 @@
         <v>242</v>
       </c>
       <c r="AH10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AI10" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="75">
       <c r="A11" s="17" t="s">
         <v>352</v>
       </c>
@@ -3002,14 +3090,11 @@
       <c r="AG11" t="s">
         <v>242</v>
       </c>
-      <c r="AH11" t="s">
-        <v>379</v>
-      </c>
       <c r="AI11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="75">
       <c r="A12" s="17" t="s">
         <v>349</v>
       </c>
@@ -3064,14 +3149,11 @@
       <c r="AG12" t="s">
         <v>242</v>
       </c>
-      <c r="AH12" t="s">
-        <v>379</v>
-      </c>
       <c r="AI12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="75">
       <c r="A13" s="17" t="s">
         <v>337</v>
       </c>
@@ -3091,7 +3173,7 @@
         <v>360</v>
       </c>
       <c r="G13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H13" t="s">
         <v>353</v>
@@ -3126,14 +3208,11 @@
       <c r="AG13" t="s">
         <v>242</v>
       </c>
-      <c r="AH13" t="s">
-        <v>379</v>
-      </c>
       <c r="AI13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="75">
       <c r="A14" s="17" t="s">
         <v>357</v>
       </c>
@@ -3153,7 +3232,7 @@
         <v>363</v>
       </c>
       <c r="G14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H14" t="s">
         <v>354</v>
@@ -3188,14 +3267,11 @@
       <c r="AG14" t="s">
         <v>242</v>
       </c>
-      <c r="AH14" t="s">
-        <v>379</v>
-      </c>
       <c r="AI14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" ht="64" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="75">
       <c r="A15" s="17" t="s">
         <v>356</v>
       </c>
@@ -3215,7 +3291,7 @@
         <v>364</v>
       </c>
       <c r="G15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H15" t="s">
         <v>355</v>
@@ -3250,11 +3326,126 @@
       <c r="AG15" t="s">
         <v>242</v>
       </c>
-      <c r="AH15" t="s">
+      <c r="AI15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="75">
+      <c r="A16" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" t="s">
         <v>379</v>
       </c>
-      <c r="AI15" t="s">
-        <v>238</v>
+      <c r="C16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" t="s">
+        <v>380</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="F16" t="s">
+        <v>382</v>
+      </c>
+      <c r="G16" t="s">
+        <v>381</v>
+      </c>
+      <c r="H16" t="s">
+        <v>379</v>
+      </c>
+      <c r="I16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J16" t="s">
+        <v>380</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="L16" t="s">
+        <v>382</v>
+      </c>
+      <c r="M16" t="s">
+        <v>381</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC16" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="AD16" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" ht="75">
+      <c r="A17" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>380</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" t="s">
+        <v>387</v>
+      </c>
+      <c r="G17" t="s">
+        <v>407</v>
+      </c>
+      <c r="H17" t="s">
+        <v>386</v>
+      </c>
+      <c r="I17" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" t="s">
+        <v>380</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="L17" t="s">
+        <v>387</v>
+      </c>
+      <c r="M17" t="s">
+        <v>407</v>
+      </c>
+      <c r="N17" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC17" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="AD17" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -3302,9 +3493,15 @@
     <hyperlink ref="A15" r:id="rId32" xr:uid="{BDEDD28F-25E0-4FEC-9F29-77B2F0701D15}"/>
     <hyperlink ref="E15" r:id="rId33" xr:uid="{6EA9E125-DA9A-4D27-A615-CFBED67ACCB2}"/>
     <hyperlink ref="K15" r:id="rId34" xr:uid="{C4972275-C907-4488-902A-0F1A94D8A3F2}"/>
+    <hyperlink ref="A16" r:id="rId35" xr:uid="{DE01F2EC-5DB6-41D4-B5BC-5CCE8FCDC077}"/>
+    <hyperlink ref="E16" r:id="rId36" xr:uid="{A7326668-E438-4CE3-BBC9-7853C5F6C148}"/>
+    <hyperlink ref="K16" r:id="rId37" xr:uid="{C7D00E6C-7F91-4EA4-A28C-357ACB9764CF}"/>
+    <hyperlink ref="A17" r:id="rId38" xr:uid="{CAA63FC6-38EE-4B1F-8C29-AA742B7B68B5}"/>
+    <hyperlink ref="E17" r:id="rId39" xr:uid="{561E48C4-9745-48E6-9078-1DE29151E2F7}"/>
+    <hyperlink ref="K17" r:id="rId40" xr:uid="{BDAB2656-CEA0-4A82-AB11-CEA413882AE1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId35"/>
+  <pageSetup orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -3313,22 +3510,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.1640625" customWidth="1"/>
+    <col min="6" max="6" width="232.140625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
@@ -3343,7 +3540,7 @@
       <c r="H1" s="45"/>
       <c r="I1" s="45"/>
     </row>
-    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="44.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -3375,7 +3572,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="90" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -3404,7 +3601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -3430,7 +3627,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -3456,7 +3653,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="18">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -3482,7 +3679,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -3508,7 +3705,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -3537,7 +3734,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16.5">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3566,7 +3763,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="14.1" customHeight="1">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3592,7 +3789,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3621,7 +3818,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3650,7 +3847,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3676,7 +3873,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3705,7 +3902,10 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
+      <c r="A15" s="34" t="s">
+        <v>325</v>
+      </c>
       <c r="B15" t="s">
         <v>318</v>
       </c>
@@ -3731,7 +3931,25 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
+      <c r="A16" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" t="s">
+        <v>312</v>
+      </c>
+      <c r="E16" t="s">
+        <v>313</v>
+      </c>
+      <c r="F16" t="s">
+        <v>392</v>
+      </c>
       <c r="G16" t="s">
         <v>368</v>
       </c>
@@ -3739,10 +3957,25 @@
         <v>46140</v>
       </c>
       <c r="J16" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="B17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C17" t="s">
+        <v>393</v>
+      </c>
+      <c r="D17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E17" t="s">
+        <v>313</v>
+      </c>
       <c r="G17" t="s">
         <v>369</v>
       </c>
@@ -3750,10 +3983,28 @@
         <v>46141</v>
       </c>
       <c r="J17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B18" t="s">
+        <v>390</v>
+      </c>
+      <c r="C18" t="s">
+        <v>394</v>
+      </c>
+      <c r="D18" t="s">
+        <v>312</v>
+      </c>
+      <c r="E18" t="s">
+        <v>313</v>
+      </c>
+      <c r="F18" t="s">
+        <v>395</v>
+      </c>
       <c r="G18" t="s">
         <v>370</v>
       </c>
@@ -3761,40 +4012,131 @@
         <v>46143</v>
       </c>
       <c r="J18" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="19" spans="7:10" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" t="s">
+        <v>353</v>
+      </c>
+      <c r="C19" t="s">
+        <v>396</v>
+      </c>
+      <c r="D19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E19" t="s">
+        <v>313</v>
+      </c>
       <c r="G19" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="H19" s="22">
         <v>46143</v>
       </c>
       <c r="J19" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" spans="7:10" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" t="s">
+        <v>354</v>
+      </c>
+      <c r="C20" t="s">
+        <v>398</v>
+      </c>
+      <c r="D20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E20" t="s">
+        <v>313</v>
+      </c>
+      <c r="F20" t="s">
+        <v>399</v>
+      </c>
       <c r="G20" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H20" s="22">
         <v>46143</v>
       </c>
       <c r="J20" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B21" t="s">
+        <v>355</v>
+      </c>
       <c r="G21" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H21" s="22">
         <v>46143</v>
       </c>
       <c r="J21" t="s">
-        <v>374</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" t="s">
+        <v>401</v>
+      </c>
+      <c r="C22" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" t="s">
+        <v>312</v>
+      </c>
+      <c r="E22" t="s">
+        <v>313</v>
+      </c>
+      <c r="G22" t="s">
+        <v>405</v>
+      </c>
+      <c r="H22" s="22">
+        <v>46147</v>
+      </c>
+      <c r="J22" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B23" t="s">
+        <v>402</v>
+      </c>
+      <c r="C23" t="s">
+        <v>404</v>
+      </c>
+      <c r="D23" t="s">
+        <v>312</v>
+      </c>
+      <c r="E23" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" t="s">
+        <v>406</v>
+      </c>
+      <c r="H23" s="22">
+        <v>46147</v>
+      </c>
+      <c r="J23" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3810,6 +4152,15 @@
     <hyperlink ref="A12" r:id="rId5" xr:uid="{3EA5242D-920D-604D-B0E9-6F5ADEE2537F}"/>
     <hyperlink ref="G13" r:id="rId6" xr:uid="{C04B92CB-055B-1549-9C7C-1350ECD0911C}"/>
     <hyperlink ref="A14" r:id="rId7" xr:uid="{2C09A1EA-369C-3D42-B213-0F809E3A2ED0}"/>
+    <hyperlink ref="A15" r:id="rId8" xr:uid="{22B19475-E163-4D0E-9614-A371ABD0BE47}"/>
+    <hyperlink ref="A16" r:id="rId9" xr:uid="{B42ECF61-FED0-4329-AE56-83B68070B72B}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{36EA5467-9125-4F0E-BBB0-16DE88C3A453}"/>
+    <hyperlink ref="A18" r:id="rId11" xr:uid="{C42558A5-4556-48FF-A90E-94C8FA9EBF4B}"/>
+    <hyperlink ref="A19" r:id="rId12" xr:uid="{123FB851-094A-423B-B728-A80019B3BFFD}"/>
+    <hyperlink ref="A20" r:id="rId13" xr:uid="{F8D551CE-9E8D-48D6-89EC-E63D716488D2}"/>
+    <hyperlink ref="A21" r:id="rId14" xr:uid="{7B2BD6BA-4610-49E5-B461-29A7E393624A}"/>
+    <hyperlink ref="A22" r:id="rId15" xr:uid="{0399CCF8-8CDB-4A65-9873-481B176BA0B4}"/>
+    <hyperlink ref="A23" r:id="rId16" xr:uid="{D1C1D669-7EE2-44CE-A254-E647034C302F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3822,7 +4173,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3853,7 +4204,7 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="21.95" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>61</v>
       </c>
@@ -3902,7 +4253,7 @@
       <c r="AD1" s="45"/>
       <c r="AE1" s="45"/>
     </row>
-    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -3997,7 +4348,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="72" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -4113,9 +4464,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -4123,19 +4474,19 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="21.95" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>116</v>
       </c>
@@ -4167,7 +4518,7 @@
       <c r="Q1" s="45"/>
       <c r="R1" s="45"/>
     </row>
-    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -4223,7 +4574,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="95.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -4279,7 +4630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="105">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -4317,7 +4668,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="165">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -4355,7 +4706,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="165">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -4393,7 +4744,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="128" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="135">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -4431,7 +4782,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="160" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="180">
       <c r="A8" t="s">
         <v>338</v>
       </c>
@@ -4469,7 +4820,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="144" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="150">
       <c r="A9" t="s">
         <v>343</v>
       </c>
@@ -4504,12 +4855,12 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="128" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="135">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -4547,7 +4898,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="75">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -4601,107 +4952,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="27.95" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="27.95" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="36" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="27.95" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="36" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="27.95" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="90.95" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="27.95" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="36" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="27.95" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="90.95" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="27.95" customHeight="1">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="63" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="27.95" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="63" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="27.95" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="63" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="27.95" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>

--- a/qms/QMS_HAOD.xlsx
+++ b/qms/QMS_HAOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{57642275-3734-42A7-AB65-B6394FB0BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A39A6A4B-817E-410C-BDBF-A41C11F49C32}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929C9972-466A-6F4E-8F6E-EEC0353A584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="24420" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="409">
   <si>
     <t>ID</t>
   </si>
@@ -1368,9 +1368,6 @@
     <t>A. Sultan Tiwana, 2026-04-28</t>
   </si>
   <si>
-    <t>Proposed</t>
-  </si>
-  <si>
     <t>My independent work — not copied from any Reference Source. — A. Sultan Tiwana, 2026-04-28</t>
   </si>
   <si>
@@ -1527,9 +1524,6 @@
     <t>StagingOntology</t>
   </si>
   <si>
-    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a paticular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
-  </si>
-  <si>
     <t>skos:altLabel (Phone Number)</t>
   </si>
   <si>
@@ -1606,6 +1600,15 @@
   </si>
   <si>
     <t>An Information Content Entity (ICE) that consists of a unique address assigned to a person, enabling the sending and receiving of electronic messages through a mail server over the network.</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a particular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
+  </si>
+  <si>
+    <t>My independent work — not copied from any Reference Source. — J. Schoening, 2026-05-09</t>
+  </si>
+  <si>
+    <t>a844c4e3e30a311a64dd48842df87ecf013e1921</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1618,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1975,6 +1978,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1983,7 +1987,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2015,10 +2018,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2310,18 +2309,18 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AI17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="37.42578125" customWidth="1"/>
+    <col min="12" max="12" width="37.5" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="16" hidden="1" customWidth="1"/>
@@ -2331,23 +2330,23 @@
     <col min="19" max="19" width="22" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="36" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="22" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.85546875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="34.28515625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="21.140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="34.33203125" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="21.1640625" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="16" style="25" customWidth="1"/>
     <col min="30" max="30" width="22" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
     <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="16.140625" customWidth="1"/>
+    <col min="34" max="34" width="16.1640625" customWidth="1"/>
     <col min="35" max="35" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="21.95" customHeight="1">
+    <row r="1" spans="1:35" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -2358,45 +2357,45 @@
       <c r="H1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="41" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
       <c r="AC1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
       <c r="AG1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="45"/>
+      <c r="AH1" s="41"/>
       <c r="AI1" s="40" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="41.1" customHeight="1">
+    <row r="2" spans="1:35" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="72.95" customHeight="1">
+    <row r="3" spans="1:35" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2589,7 +2588,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="60">
+    <row r="4" spans="1:35" ht="65" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>246</v>
       </c>
@@ -2651,7 +2650,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="90">
+    <row r="5" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>247</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="60">
+    <row r="6" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
         <v>279</v>
       </c>
@@ -2778,7 +2777,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="60">
+    <row r="7" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
         <v>280</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="105">
+    <row r="8" spans="1:35" ht="96" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>298</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="60">
+    <row r="9" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
         <v>325</v>
       </c>
@@ -2973,12 +2972,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="75">
+    <row r="10" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C10" t="s">
         <v>209</v>
@@ -2990,13 +2989,13 @@
         <v>315</v>
       </c>
       <c r="F10" t="s">
+        <v>330</v>
+      </c>
+      <c r="G10" t="s">
         <v>331</v>
       </c>
-      <c r="G10" t="s">
-        <v>332</v>
-      </c>
       <c r="H10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I10" t="s">
         <v>209</v>
@@ -3008,13 +3007,13 @@
         <v>315</v>
       </c>
       <c r="L10" t="s">
+        <v>330</v>
+      </c>
+      <c r="M10" t="s">
         <v>331</v>
       </c>
-      <c r="M10" t="s">
-        <v>332</v>
-      </c>
       <c r="N10" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AC10" s="25" t="s">
         <v>327</v>
@@ -3029,18 +3028,18 @@
         <v>242</v>
       </c>
       <c r="AH10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AI10" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="75">
+    <row r="11" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C11" t="s">
         <v>209</v>
@@ -3052,13 +3051,13 @@
         <v>315</v>
       </c>
       <c r="F11" t="s">
+        <v>333</v>
+      </c>
+      <c r="G11" t="s">
+        <v>335</v>
+      </c>
+      <c r="H11" t="s">
         <v>334</v>
-      </c>
-      <c r="G11" t="s">
-        <v>336</v>
-      </c>
-      <c r="H11" t="s">
-        <v>335</v>
       </c>
       <c r="I11" t="s">
         <v>209</v>
@@ -3070,16 +3069,16 @@
         <v>315</v>
       </c>
       <c r="L11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AD11" s="25" t="s">
         <v>244</v>
@@ -3090,16 +3089,19 @@
       <c r="AG11" t="s">
         <v>242</v>
       </c>
+      <c r="AH11" t="s">
+        <v>408</v>
+      </c>
       <c r="AI11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C12" t="s">
         <v>209</v>
@@ -3111,13 +3113,13 @@
         <v>315</v>
       </c>
       <c r="F12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
         <v>209</v>
@@ -3129,16 +3131,16 @@
         <v>315</v>
       </c>
       <c r="L12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AC12" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AD12" s="25" t="s">
         <v>244</v>
@@ -3149,16 +3151,19 @@
       <c r="AG12" t="s">
         <v>242</v>
       </c>
+      <c r="AH12" t="s">
+        <v>408</v>
+      </c>
       <c r="AI12" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C13" t="s">
         <v>209</v>
@@ -3170,13 +3175,13 @@
         <v>315</v>
       </c>
       <c r="F13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I13" t="s">
         <v>209</v>
@@ -3188,16 +3193,16 @@
         <v>315</v>
       </c>
       <c r="L13" t="s">
+        <v>359</v>
+      </c>
+      <c r="M13" t="s">
         <v>360</v>
       </c>
-      <c r="M13" t="s">
-        <v>361</v>
-      </c>
       <c r="N13" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AC13" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AD13" s="25" t="s">
         <v>244</v>
@@ -3208,16 +3213,19 @@
       <c r="AG13" t="s">
         <v>242</v>
       </c>
+      <c r="AH13" t="s">
+        <v>408</v>
+      </c>
       <c r="AI13" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C14" t="s">
         <v>209</v>
@@ -3229,13 +3237,13 @@
         <v>315</v>
       </c>
       <c r="F14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I14" t="s">
         <v>209</v>
@@ -3247,16 +3255,16 @@
         <v>315</v>
       </c>
       <c r="L14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N14" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AC14" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AD14" s="25" t="s">
         <v>244</v>
@@ -3267,16 +3275,19 @@
       <c r="AG14" t="s">
         <v>242</v>
       </c>
+      <c r="AH14" t="s">
+        <v>408</v>
+      </c>
       <c r="AI14" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C15" t="s">
         <v>209</v>
@@ -3288,13 +3299,13 @@
         <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I15" t="s">
         <v>209</v>
@@ -3306,16 +3317,16 @@
         <v>315</v>
       </c>
       <c r="L15" t="s">
+        <v>363</v>
+      </c>
+      <c r="M15" t="s">
         <v>364</v>
       </c>
-      <c r="M15" t="s">
-        <v>365</v>
-      </c>
       <c r="N15" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AC15" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AD15" s="25" t="s">
         <v>244</v>
@@ -3326,55 +3337,58 @@
       <c r="AG15" t="s">
         <v>242</v>
       </c>
+      <c r="AH15" t="s">
+        <v>408</v>
+      </c>
       <c r="AI15" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B16" t="s">
         <v>378</v>
-      </c>
-      <c r="B16" t="s">
-        <v>379</v>
       </c>
       <c r="C16" t="s">
         <v>209</v>
       </c>
       <c r="D16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="F16" t="s">
         <v>380</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="F16" t="s">
-        <v>382</v>
-      </c>
       <c r="G16" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="H16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I16" t="s">
         <v>209</v>
       </c>
       <c r="J16" t="s">
+        <v>379</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="L16" t="s">
         <v>380</v>
       </c>
-      <c r="K16" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
+        <v>406</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="AC16" s="25" t="s">
         <v>382</v>
-      </c>
-      <c r="M16" t="s">
-        <v>381</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC16" s="25" t="s">
-        <v>384</v>
       </c>
       <c r="AD16" s="25" t="s">
         <v>244</v>
@@ -3385,55 +3399,58 @@
       <c r="AG16" t="s">
         <v>242</v>
       </c>
+      <c r="AH16" t="s">
+        <v>408</v>
+      </c>
       <c r="AI16" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" ht="75">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C17" t="s">
         <v>209</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="F17" t="s">
         <v>385</v>
       </c>
-      <c r="F17" t="s">
-        <v>387</v>
-      </c>
       <c r="G17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I17" t="s">
         <v>209</v>
       </c>
       <c r="J17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K17" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="L17" t="s">
         <v>385</v>
       </c>
-      <c r="L17" t="s">
-        <v>387</v>
-      </c>
       <c r="M17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N17" s="25" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AC17" s="25" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AD17" s="25" t="s">
         <v>244</v>
@@ -3444,8 +3461,11 @@
       <c r="AG17" t="s">
         <v>242</v>
       </c>
+      <c r="AH17" t="s">
+        <v>408</v>
+      </c>
       <c r="AI17" t="s">
-        <v>328</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3511,36 +3531,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="232.140625" customWidth="1"/>
+    <col min="6" max="6" width="232.1640625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="13" style="22" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
       <c r="D1" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-    </row>
-    <row r="2" spans="1:10" ht="44.1" customHeight="1">
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+    </row>
+    <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -3572,7 +3592,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1">
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -3601,7 +3621,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>166</v>
       </c>
@@ -3627,7 +3647,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -3653,7 +3673,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>176</v>
       </c>
@@ -3679,7 +3699,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>175</v>
       </c>
@@ -3705,7 +3725,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="23" t="s">
         <v>187</v>
       </c>
@@ -3734,7 +3754,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5">
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>175</v>
       </c>
@@ -3763,7 +3783,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.1" customHeight="1">
+    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>187</v>
       </c>
@@ -3789,7 +3809,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1">
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>246</v>
       </c>
@@ -3818,7 +3838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>247</v>
       </c>
@@ -3847,7 +3867,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>263</v>
       </c>
@@ -3873,7 +3893,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>298</v>
       </c>
@@ -3893,7 +3913,7 @@
         <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H14" s="22">
         <v>46134</v>
@@ -3902,7 +3922,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="34" t="s">
         <v>325</v>
       </c>
@@ -3922,7 +3942,7 @@
         <v>320</v>
       </c>
       <c r="G15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H15" s="22">
         <v>46135</v>
@@ -3931,15 +3951,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C16" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D16" t="s">
         <v>312</v>
@@ -3948,27 +3968,27 @@
         <v>313</v>
       </c>
       <c r="F16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H16" s="22">
         <v>46140</v>
       </c>
       <c r="J16" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D17" t="s">
         <v>312</v>
@@ -3977,24 +3997,24 @@
         <v>313</v>
       </c>
       <c r="G17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H17" s="22">
         <v>46141</v>
       </c>
       <c r="J17" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B18" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D18" t="s">
         <v>312</v>
@@ -4003,27 +4023,27 @@
         <v>313</v>
       </c>
       <c r="F18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G18" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H18" s="22">
         <v>46143</v>
       </c>
       <c r="J18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D19" t="s">
         <v>312</v>
@@ -4032,24 +4052,24 @@
         <v>313</v>
       </c>
       <c r="G19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H19" s="22">
         <v>46143</v>
       </c>
       <c r="J19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
@@ -4058,44 +4078,44 @@
         <v>313</v>
       </c>
       <c r="F20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H20" s="22">
         <v>46143</v>
       </c>
       <c r="J20" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G21" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H21" s="22">
         <v>46143</v>
       </c>
       <c r="J21" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B22" t="s">
+        <v>399</v>
+      </c>
+      <c r="C22" t="s">
         <v>401</v>
-      </c>
-      <c r="C22" t="s">
-        <v>403</v>
       </c>
       <c r="D22" t="s">
         <v>312</v>
@@ -4104,24 +4124,24 @@
         <v>313</v>
       </c>
       <c r="G22" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H22" s="22">
         <v>46147</v>
       </c>
       <c r="J22" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="B23" t="s">
         <v>400</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>402</v>
-      </c>
-      <c r="C23" t="s">
-        <v>404</v>
       </c>
       <c r="D23" t="s">
         <v>312</v>
@@ -4130,13 +4150,13 @@
         <v>313</v>
       </c>
       <c r="G23" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H23" s="22">
         <v>46147</v>
       </c>
       <c r="J23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4173,7 +4193,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -4204,56 +4224,56 @@
     <col min="30" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="21.95" customHeight="1">
+    <row r="1" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
       <c r="F1" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
       <c r="O1" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
       <c r="T1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
       <c r="Y1" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="45"/>
+      <c r="Z1" s="41"/>
       <c r="AA1" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="45"/>
+      <c r="AB1" s="41"/>
       <c r="AC1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-    </row>
-    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1">
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+    </row>
+    <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -4348,7 +4368,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="72" customHeight="1">
+    <row r="3" spans="1:31" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
@@ -4464,9 +4484,9 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" style="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -4474,51 +4494,51 @@
     <col min="6" max="6" width="13" style="22" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="45" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="41.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="45" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21.95" customHeight="1">
+    <row r="1" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
       <c r="D1" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
       <c r="G1" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
       <c r="M1" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
       <c r="P1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-    </row>
-    <row r="2" spans="1:18" ht="36.950000000000003" customHeight="1">
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+    </row>
+    <row r="2" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
@@ -4574,7 +4594,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="95.1" customHeight="1">
+    <row r="3" spans="1:18" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>163</v>
       </c>
@@ -4630,7 +4650,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="105">
+    <row r="4" spans="1:18" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -4668,7 +4688,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="165">
+    <row r="5" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -4706,7 +4726,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="165">
+    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>268</v>
       </c>
@@ -4744,7 +4764,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="135">
+    <row r="7" spans="1:18" ht="128" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -4782,33 +4802,33 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="180">
+    <row r="8" spans="1:18" ht="160" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B8" s="22">
         <v>46142</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F8" s="22">
         <v>46142</v>
       </c>
       <c r="G8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P8" t="s">
         <v>171</v>
@@ -4817,33 +4837,36 @@
         <v>244</v>
       </c>
       <c r="R8" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="150">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="144" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B9" s="22">
         <v>46142</v>
       </c>
       <c r="C9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" t="s">
         <v>345</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="25" t="s">
         <v>346</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>347</v>
       </c>
       <c r="F9" s="22">
         <v>46142</v>
       </c>
       <c r="G9" t="s">
+        <v>345</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>346</v>
       </c>
-      <c r="H9" s="25" t="s">
-        <v>347</v>
+      <c r="I9" s="25" t="s">
+        <v>407</v>
       </c>
       <c r="P9" t="s">
         <v>171</v>
@@ -4852,15 +4875,15 @@
         <v>244</v>
       </c>
       <c r="R9" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="135">
+    <row r="13" spans="1:18" ht="128" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -4898,7 +4921,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75">
+    <row r="14" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -4921,7 +4944,7 @@
         <v>303</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I14" s="38" t="s">
         <v>295</v>
@@ -4952,107 +4975,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.95" customHeight="1">
+    <row r="1" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="27.95" customHeight="1">
+    <row r="3" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="36" customHeight="1">
+    <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="27.95" customHeight="1">
+    <row r="5" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="36" customHeight="1">
+    <row r="6" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="27.95" customHeight="1">
+    <row r="7" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="90.95" customHeight="1">
+    <row r="8" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="27.95" customHeight="1">
+    <row r="9" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="36" customHeight="1">
+    <row r="10" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="27.95" customHeight="1">
+    <row r="11" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="90.95" customHeight="1">
+    <row r="12" spans="1:1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="27.95" customHeight="1">
+    <row r="13" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="63" customHeight="1">
+    <row r="14" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27.95" customHeight="1">
+    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="63" customHeight="1">
+    <row r="16" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27.95" customHeight="1">
+    <row r="17" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="63" customHeight="1">
+    <row r="18" spans="1:1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="27.95" customHeight="1">
+    <row r="19" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="36" customHeight="1">
+    <row r="20" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>156</v>
       </c>
